--- a/Modelo/datos/Raw_Data/Matriz_de_Adyacencia_Pensiones_v5.xlsx
+++ b/Modelo/datos/Raw_Data/Matriz_de_Adyacencia_Pensiones_v5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a7d57e8591b932/Escritorio/CICS/2025/Tesis/Objetivos de Aprendizaje/Modelo/datos/Raw_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="559" documentId="8_{00D88C31-2993-4F88-955D-B3AEA2AC3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62976A8-BA5E-403D-9CF4-46E3EF02C3DB}"/>
+  <xr:revisionPtr revIDLastSave="569" documentId="8_{00D88C31-2993-4F88-955D-B3AEA2AC3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1198A54-78C5-4CA2-BAA5-BF5B8A21E24B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E85862A8-A9B5-4BB7-B4AF-3D0252E6C1A3}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$BR$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$BT$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="83">
   <si>
     <t>Que_es_pension</t>
   </si>
@@ -284,13 +284,27 @@
   <si>
     <t>Tasa_Interes_RV</t>
   </si>
+  <si>
+    <t>Jubilación</t>
+  </si>
+  <si>
+    <t>Rentabilidad</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -347,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -358,11 +372,54 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1046,10 +1103,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -1367,1096 +1420,1179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}">
-  <dimension ref="A1:BR70"/>
+  <dimension ref="A1:BT72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.59765625" customWidth="1"/>
-    <col min="2" max="3" width="11.3984375" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" customWidth="1"/>
-    <col min="5" max="10" width="11.3984375" customWidth="1"/>
-    <col min="11" max="11" width="13.86328125" customWidth="1"/>
-    <col min="12" max="16" width="11.3984375" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" customWidth="1"/>
-    <col min="18" max="18" width="11.3984375" customWidth="1"/>
+    <col min="1" max="3" width="27.59765625" customWidth="1"/>
+    <col min="4" max="5" width="11.3984375" customWidth="1"/>
+    <col min="6" max="6" width="10.86328125" customWidth="1"/>
+    <col min="7" max="12" width="11.3984375" customWidth="1"/>
+    <col min="13" max="13" width="13.86328125" customWidth="1"/>
+    <col min="14" max="18" width="11.3984375" customWidth="1"/>
     <col min="19" max="19" width="10.86328125" customWidth="1"/>
-    <col min="20" max="23" width="11.3984375" customWidth="1"/>
-    <col min="24" max="25" width="10.86328125" customWidth="1"/>
-    <col min="26" max="26" width="13.265625" customWidth="1"/>
-    <col min="27" max="27" width="13.59765625" customWidth="1"/>
-    <col min="28" max="44" width="11.3984375" customWidth="1"/>
-    <col min="45" max="45" width="13.86328125" customWidth="1"/>
-    <col min="46" max="58" width="11.3984375" customWidth="1"/>
-    <col min="59" max="65" width="10.86328125" customWidth="1"/>
-    <col min="66" max="69" width="11.3984375" customWidth="1"/>
-    <col min="70" max="71" width="10.86328125" customWidth="1"/>
-    <col min="72" max="72" width="11.3984375" customWidth="1"/>
+    <col min="20" max="20" width="11.3984375" customWidth="1"/>
+    <col min="21" max="21" width="10.86328125" customWidth="1"/>
+    <col min="22" max="25" width="11.3984375" customWidth="1"/>
+    <col min="26" max="27" width="10.86328125" customWidth="1"/>
+    <col min="28" max="28" width="13.265625" customWidth="1"/>
+    <col min="29" max="29" width="13.59765625" customWidth="1"/>
+    <col min="30" max="46" width="11.3984375" customWidth="1"/>
+    <col min="47" max="47" width="13.86328125" customWidth="1"/>
+    <col min="48" max="60" width="11.3984375" customWidth="1"/>
+    <col min="61" max="67" width="10.86328125" customWidth="1"/>
+    <col min="68" max="71" width="11.3984375" customWidth="1"/>
+    <col min="72" max="73" width="10.86328125" customWidth="1"/>
+    <col min="74" max="74" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="57.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:72" ht="57" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>77</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>78</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>80</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+    </row>
+    <row r="3" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1"/>
+      <c r="BE3" s="1"/>
+      <c r="BF3" s="1"/>
+      <c r="BG3" s="1"/>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1"/>
+      <c r="BJ3" s="1"/>
+      <c r="BK3" s="1"/>
+      <c r="BL3" s="1"/>
+      <c r="BM3" s="1"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="1"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="1"/>
+      <c r="BS3" s="1"/>
+      <c r="BT3" s="1"/>
+    </row>
+    <row r="4" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2">
-        <v>1</v>
-      </c>
-      <c r="U2" s="2">
-        <v>1</v>
-      </c>
-      <c r="V2" s="2">
-        <v>1</v>
-      </c>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AL2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BA2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BG2" s="2"/>
-      <c r="BH2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BI2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK2" s="2"/>
-      <c r="BL2" s="2"/>
-      <c r="BM2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BN2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ2" s="2">
-        <v>1</v>
-      </c>
-      <c r="BR2" s="2"/>
-    </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2">
+        <v>1</v>
+      </c>
+      <c r="W4" s="2">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BK4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BL4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BP4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BQ4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BR4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BT4" s="2"/>
+    </row>
+    <row r="5" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>76</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AS3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>58</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    </row>
+    <row r="7" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AG5">
-        <v>1</v>
-      </c>
-      <c r="AI5">
-        <v>1</v>
-      </c>
-      <c r="AQ5">
-        <v>1</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AV5">
-        <v>1</v>
-      </c>
-      <c r="AW5">
-        <v>1</v>
-      </c>
-      <c r="AZ5">
-        <v>1</v>
-      </c>
-      <c r="BH5">
-        <v>1</v>
-      </c>
-      <c r="BO5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="BB7">
+        <v>1</v>
+      </c>
+      <c r="BJ7">
+        <v>1</v>
+      </c>
+      <c r="BQ7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6">
-        <v>1</v>
-      </c>
-      <c r="AL6">
-        <v>1</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AV6">
-        <v>1</v>
-      </c>
-      <c r="AW6">
-        <v>1</v>
-      </c>
-      <c r="AZ6">
-        <v>1</v>
-      </c>
-      <c r="BP6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>1</v>
+      </c>
+      <c r="BR8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AI7">
-        <v>1</v>
-      </c>
-      <c r="AV7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AX9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR8" s="2"/>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BA8" s="2"/>
-      <c r="BB8" s="2"/>
-      <c r="BC8" s="2"/>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE8" s="2"/>
-      <c r="BF8" s="2"/>
-      <c r="BG8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BH8" s="2"/>
-      <c r="BI8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ8" s="2"/>
-      <c r="BK8" s="2"/>
-      <c r="BL8" s="2"/>
-      <c r="BM8" s="2"/>
-      <c r="BN8" s="2"/>
-      <c r="BO8" s="2"/>
-      <c r="BP8" s="2"/>
-      <c r="BQ8" s="2"/>
-      <c r="BR8" s="2"/>
-    </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="2"/>
+      <c r="AL10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="2"/>
+      <c r="AN10" s="2"/>
+      <c r="AO10" s="2"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+      <c r="AR10" s="2"/>
+      <c r="AS10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="2"/>
+      <c r="AU10" s="2"/>
+      <c r="AV10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="2"/>
+      <c r="AX10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY10" s="2"/>
+      <c r="AZ10" s="2"/>
+      <c r="BA10" s="2"/>
+      <c r="BB10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="2"/>
+      <c r="BD10" s="2"/>
+      <c r="BE10" s="2"/>
+      <c r="BF10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BG10" s="2"/>
+      <c r="BH10" s="2"/>
+      <c r="BI10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BJ10" s="2"/>
+      <c r="BK10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BL10" s="2"/>
+      <c r="BM10" s="2"/>
+      <c r="BN10" s="2"/>
+      <c r="BO10" s="2"/>
+      <c r="BP10" s="2"/>
+      <c r="BQ10" s="2"/>
+      <c r="BR10" s="2"/>
+      <c r="BS10" s="2"/>
+      <c r="BT10" s="2"/>
+    </row>
+    <row r="11" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AI9">
-        <v>1</v>
-      </c>
-      <c r="AJ9">
-        <v>1</v>
-      </c>
-      <c r="AK9">
-        <v>1</v>
-      </c>
-      <c r="AP9">
-        <v>1</v>
-      </c>
-      <c r="AQ9">
-        <v>1</v>
-      </c>
-      <c r="AR9">
-        <v>1</v>
-      </c>
-      <c r="AS9">
-        <v>1</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AV9">
-        <v>1</v>
-      </c>
-      <c r="AW9">
-        <v>1</v>
-      </c>
-      <c r="AY9">
-        <v>1</v>
-      </c>
-      <c r="BB9">
-        <v>1</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="BE9">
-        <v>1</v>
-      </c>
-      <c r="BF9">
-        <v>1</v>
-      </c>
-      <c r="BI9">
-        <v>1</v>
-      </c>
-      <c r="BL9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>1</v>
+      </c>
+      <c r="AS11">
+        <v>1</v>
+      </c>
+      <c r="AT11">
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>1</v>
+      </c>
+      <c r="AV11">
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
+      <c r="BA11">
+        <v>1</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BF11">
+        <v>1</v>
+      </c>
+      <c r="BG11">
+        <v>1</v>
+      </c>
+      <c r="BH11">
+        <v>1</v>
+      </c>
+      <c r="BK11">
+        <v>1</v>
+      </c>
+      <c r="BN11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>2</v>
       </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>1</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="BN10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="BP12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>72</v>
       </c>
-      <c r="BJ12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3">
-        <v>1</v>
-      </c>
-      <c r="P13" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="3"/>
-      <c r="AT13" s="3"/>
-      <c r="AU13" s="3"/>
-      <c r="AV13" s="3"/>
-      <c r="AW13" s="3"/>
-      <c r="AX13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AY13" s="3"/>
-      <c r="AZ13" s="3"/>
-      <c r="BA13" s="3"/>
-      <c r="BB13" s="3"/>
-      <c r="BC13" s="3"/>
-      <c r="BD13" s="3"/>
-      <c r="BE13" s="3"/>
-      <c r="BF13" s="3"/>
-      <c r="BG13" s="3"/>
-      <c r="BH13" s="3"/>
-      <c r="BI13" s="3"/>
-      <c r="BJ13" s="3"/>
-      <c r="BK13" s="3"/>
-      <c r="BL13" s="3"/>
-      <c r="BM13" s="3"/>
-      <c r="BN13" s="3"/>
-      <c r="BO13" s="3"/>
-      <c r="BP13" s="3"/>
-      <c r="BQ13" s="3"/>
-      <c r="BR13" s="3"/>
-    </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+      <c r="BL14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3">
+        <v>1</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1</v>
+      </c>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="3"/>
+      <c r="AT15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="3"/>
+      <c r="AV15" s="3"/>
+      <c r="AW15" s="3"/>
+      <c r="AX15" s="3"/>
+      <c r="AY15" s="3"/>
+      <c r="AZ15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BA15" s="3"/>
+      <c r="BB15" s="3"/>
+      <c r="BC15" s="3"/>
+      <c r="BD15" s="3"/>
+      <c r="BE15" s="3"/>
+      <c r="BF15" s="3"/>
+      <c r="BG15" s="3"/>
+      <c r="BH15" s="3"/>
+      <c r="BI15" s="3"/>
+      <c r="BJ15" s="3"/>
+      <c r="BK15" s="3"/>
+      <c r="BL15" s="3"/>
+      <c r="BM15" s="3"/>
+      <c r="BN15" s="3"/>
+      <c r="BO15" s="3"/>
+      <c r="BP15" s="3"/>
+      <c r="BQ15" s="3"/>
+      <c r="BR15" s="3"/>
+      <c r="BS15" s="3"/>
+      <c r="BT15" s="3"/>
+    </row>
+    <row r="16" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2">
-        <v>1</v>
-      </c>
-      <c r="P14" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>1</v>
-      </c>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2">
-        <v>1</v>
-      </c>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-      <c r="AI14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
-      <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
-      <c r="AP14" s="2"/>
-      <c r="AQ14" s="2"/>
-      <c r="AR14" s="2"/>
-      <c r="AS14" s="2"/>
-      <c r="AT14" s="2"/>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="AY14" s="2"/>
-      <c r="AZ14" s="2"/>
-      <c r="BA14" s="2"/>
-      <c r="BB14" s="2"/>
-      <c r="BC14" s="2"/>
-      <c r="BD14" s="2"/>
-      <c r="BE14" s="2"/>
-      <c r="BF14" s="2"/>
-      <c r="BG14" s="2"/>
-      <c r="BH14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BI14" s="2"/>
-      <c r="BJ14" s="2"/>
-      <c r="BK14" s="2"/>
-      <c r="BL14" s="2"/>
-      <c r="BM14" s="2"/>
-      <c r="BN14" s="2"/>
-      <c r="BO14" s="2"/>
-      <c r="BP14" s="2"/>
-      <c r="BQ14" s="2"/>
-      <c r="BR14" s="2"/>
-    </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1</v>
+      </c>
+      <c r="S16" s="2">
+        <v>1</v>
+      </c>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+      <c r="AP16" s="2"/>
+      <c r="AQ16" s="2"/>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="2"/>
+      <c r="AT16" s="2"/>
+      <c r="AU16" s="2"/>
+      <c r="AV16" s="2"/>
+      <c r="AW16" s="2"/>
+      <c r="AX16" s="2"/>
+      <c r="AY16" s="2"/>
+      <c r="AZ16" s="2"/>
+      <c r="BA16" s="2"/>
+      <c r="BB16" s="2"/>
+      <c r="BC16" s="2"/>
+      <c r="BD16" s="2"/>
+      <c r="BE16" s="2"/>
+      <c r="BF16" s="2"/>
+      <c r="BG16" s="2"/>
+      <c r="BH16" s="2"/>
+      <c r="BI16" s="2"/>
+      <c r="BJ16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BK16" s="2"/>
+      <c r="BL16" s="2"/>
+      <c r="BM16" s="2"/>
+      <c r="BN16" s="2"/>
+      <c r="BO16" s="2"/>
+      <c r="BP16" s="2"/>
+      <c r="BQ16" s="2"/>
+      <c r="BR16" s="2"/>
+      <c r="BS16" s="2"/>
+      <c r="BT16" s="2"/>
+    </row>
+    <row r="17" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-      <c r="Z15">
-        <v>1</v>
-      </c>
-      <c r="BO15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="BQ17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+    <row r="20" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>66</v>
       </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="W18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
+    <row r="22" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="Q20">
-        <v>1</v>
-      </c>
-      <c r="U20">
-        <v>1</v>
-      </c>
-      <c r="V20">
-        <v>1</v>
-      </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2">
-        <v>1</v>
-      </c>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
-      <c r="AG21" s="2"/>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-      <c r="AQ21" s="2"/>
-      <c r="AR21" s="2"/>
-      <c r="AS21" s="2"/>
-      <c r="AT21" s="2"/>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AX21" s="2"/>
-      <c r="AY21" s="2"/>
-      <c r="AZ21" s="2"/>
-      <c r="BA21" s="2"/>
-      <c r="BB21" s="2"/>
-      <c r="BC21" s="2"/>
-      <c r="BD21" s="2"/>
-      <c r="BE21" s="2"/>
-      <c r="BF21" s="2"/>
-      <c r="BG21" s="2"/>
-      <c r="BH21" s="2"/>
-      <c r="BI21" s="2"/>
-      <c r="BJ21" s="2"/>
-      <c r="BK21" s="2"/>
-      <c r="BL21" s="2"/>
-      <c r="BM21" s="2"/>
-      <c r="BN21" s="2"/>
-      <c r="BO21" s="2"/>
-      <c r="BP21" s="2"/>
-      <c r="BQ21" s="2"/>
-      <c r="BR21" s="2"/>
-    </row>
-    <row r="22" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2480,7 +2616,9 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
+      <c r="X23" s="2">
+        <v>1</v>
+      </c>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
@@ -2527,160 +2665,93 @@
       <c r="BP23" s="2"/>
       <c r="BQ23" s="2"/>
       <c r="BR23" s="2"/>
-    </row>
-    <row r="24" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
+      <c r="BS23" s="2"/>
+      <c r="BT23" s="2"/>
+    </row>
+    <row r="24" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="2"/>
+      <c r="AL25" s="2"/>
+      <c r="AM25" s="2"/>
+      <c r="AN25" s="2"/>
+      <c r="AO25" s="2"/>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="2"/>
+      <c r="AR25" s="2"/>
+      <c r="AS25" s="2"/>
+      <c r="AT25" s="2"/>
+      <c r="AU25" s="2"/>
+      <c r="AV25" s="2"/>
+      <c r="AW25" s="2"/>
+      <c r="AX25" s="2"/>
+      <c r="AY25" s="2"/>
+      <c r="AZ25" s="2"/>
+      <c r="BA25" s="2"/>
+      <c r="BB25" s="2"/>
+      <c r="BC25" s="2"/>
+      <c r="BD25" s="2"/>
+      <c r="BE25" s="2"/>
+      <c r="BF25" s="2"/>
+      <c r="BG25" s="2"/>
+      <c r="BH25" s="2"/>
+      <c r="BI25" s="2"/>
+      <c r="BJ25" s="2"/>
+      <c r="BK25" s="2"/>
+      <c r="BL25" s="2"/>
+      <c r="BM25" s="2"/>
+      <c r="BN25" s="2"/>
+      <c r="BO25" s="2"/>
+      <c r="BP25" s="2"/>
+      <c r="BQ25" s="2"/>
+      <c r="BR25" s="2"/>
+      <c r="BS25" s="2"/>
+      <c r="BT25" s="2"/>
+    </row>
+    <row r="26" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="2"/>
-      <c r="AP24" s="2"/>
-      <c r="AQ24" s="2"/>
-      <c r="AR24" s="2"/>
-      <c r="AS24" s="2"/>
-      <c r="AT24" s="2"/>
-      <c r="AU24" s="2"/>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AX24" s="2"/>
-      <c r="AY24" s="2"/>
-      <c r="AZ24" s="2"/>
-      <c r="BA24" s="2"/>
-      <c r="BB24" s="2"/>
-      <c r="BC24" s="2"/>
-      <c r="BD24" s="2"/>
-      <c r="BE24" s="2"/>
-      <c r="BF24" s="2"/>
-      <c r="BG24" s="2"/>
-      <c r="BH24" s="2"/>
-      <c r="BI24" s="2"/>
-      <c r="BJ24" s="2"/>
-      <c r="BK24" s="2"/>
-      <c r="BL24" s="2"/>
-      <c r="BM24" s="2"/>
-      <c r="BN24" s="2"/>
-      <c r="BO24" s="2"/>
-      <c r="BP24" s="2"/>
-      <c r="BQ24" s="2"/>
-      <c r="BR24" s="2"/>
-    </row>
-    <row r="25" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="3"/>
-      <c r="AH25" s="3"/>
-      <c r="AI25" s="3"/>
-      <c r="AJ25" s="3"/>
-      <c r="AK25" s="3"/>
-      <c r="AL25" s="3"/>
-      <c r="AM25" s="3"/>
-      <c r="AN25" s="3"/>
-      <c r="AO25" s="3"/>
-      <c r="AP25" s="3"/>
-      <c r="AQ25" s="3"/>
-      <c r="AR25" s="3"/>
-      <c r="AS25" s="3"/>
-      <c r="AT25" s="3"/>
-      <c r="AU25" s="3"/>
-      <c r="AV25" s="3"/>
-      <c r="AW25" s="3"/>
-      <c r="AX25" s="3"/>
-      <c r="AY25" s="3"/>
-      <c r="AZ25" s="3"/>
-      <c r="BA25" s="3"/>
-      <c r="BB25" s="3"/>
-      <c r="BC25" s="3"/>
-      <c r="BD25" s="3"/>
-      <c r="BE25" s="3"/>
-      <c r="BF25" s="3"/>
-      <c r="BG25" s="3"/>
-      <c r="BH25" s="3"/>
-      <c r="BI25" s="3"/>
-      <c r="BJ25" s="3"/>
-      <c r="BK25" s="3"/>
-      <c r="BL25" s="3"/>
-      <c r="BM25" s="3"/>
-      <c r="BN25" s="3"/>
-      <c r="BO25" s="3"/>
-      <c r="BP25" s="3"/>
-      <c r="BQ25" s="3"/>
-      <c r="BR25" s="3"/>
-    </row>
-    <row r="26" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2707,9 +2778,7 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
-      <c r="AA26" s="2">
-        <v>1</v>
-      </c>
+      <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="2"/>
@@ -2753,1086 +2822,1092 @@
       <c r="BP26" s="2"/>
       <c r="BQ26" s="2"/>
       <c r="BR26" s="2"/>
-    </row>
-    <row r="27" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+      <c r="BS26" s="2"/>
+      <c r="BT26" s="2"/>
+    </row>
+    <row r="27" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="3"/>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="3"/>
+      <c r="AM27" s="3"/>
+      <c r="AN27" s="3"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="3"/>
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="3"/>
+      <c r="AT27" s="3"/>
+      <c r="AU27" s="3"/>
+      <c r="AV27" s="3"/>
+      <c r="AW27" s="3"/>
+      <c r="AX27" s="3"/>
+      <c r="AY27" s="3"/>
+      <c r="AZ27" s="3"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="3"/>
+      <c r="BC27" s="3"/>
+      <c r="BD27" s="3"/>
+      <c r="BE27" s="3"/>
+      <c r="BF27" s="3"/>
+      <c r="BG27" s="3"/>
+      <c r="BH27" s="3"/>
+      <c r="BI27" s="3"/>
+      <c r="BJ27" s="3"/>
+      <c r="BK27" s="3"/>
+      <c r="BL27" s="3"/>
+      <c r="BM27" s="3"/>
+      <c r="BN27" s="3"/>
+      <c r="BO27" s="3"/>
+      <c r="BP27" s="3"/>
+      <c r="BQ27" s="3"/>
+      <c r="BR27" s="3"/>
+      <c r="BS27" s="3"/>
+      <c r="BT27" s="3"/>
+    </row>
+    <row r="28" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
+      <c r="AM28" s="2"/>
+      <c r="AN28" s="2"/>
+      <c r="AO28" s="2"/>
+      <c r="AP28" s="2"/>
+      <c r="AQ28" s="2"/>
+      <c r="AR28" s="2"/>
+      <c r="AS28" s="2"/>
+      <c r="AT28" s="2"/>
+      <c r="AU28" s="2"/>
+      <c r="AV28" s="2"/>
+      <c r="AW28" s="2"/>
+      <c r="AX28" s="2"/>
+      <c r="AY28" s="2"/>
+      <c r="AZ28" s="2"/>
+      <c r="BA28" s="2"/>
+      <c r="BB28" s="2"/>
+      <c r="BC28" s="2"/>
+      <c r="BD28" s="2"/>
+      <c r="BE28" s="2"/>
+      <c r="BF28" s="2"/>
+      <c r="BG28" s="2"/>
+      <c r="BH28" s="2"/>
+      <c r="BI28" s="2"/>
+      <c r="BJ28" s="2"/>
+      <c r="BK28" s="2"/>
+      <c r="BL28" s="2"/>
+      <c r="BM28" s="2"/>
+      <c r="BN28" s="2"/>
+      <c r="BO28" s="2"/>
+      <c r="BP28" s="2"/>
+      <c r="BQ28" s="2"/>
+      <c r="BR28" s="2"/>
+      <c r="BS28" s="2"/>
+      <c r="BT28" s="2"/>
+    </row>
+    <row r="29" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="3" t="s">
+    <row r="30" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3">
-        <v>1</v>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3">
-        <v>1</v>
-      </c>
-      <c r="O28" s="3">
-        <v>1</v>
-      </c>
-      <c r="P28" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3">
-        <v>1</v>
-      </c>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
-      <c r="AF28" s="3"/>
-      <c r="AG28" s="3"/>
-      <c r="AH28" s="3"/>
-      <c r="AI28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AK28" s="3"/>
-      <c r="AL28" s="3"/>
-      <c r="AM28" s="3"/>
-      <c r="AN28" s="3"/>
-      <c r="AO28" s="3"/>
-      <c r="AP28" s="3"/>
-      <c r="AQ28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AR28" s="3"/>
-      <c r="AS28" s="3"/>
-      <c r="AT28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AU28" s="3"/>
-      <c r="AV28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AW28" s="3"/>
-      <c r="AX28" s="3"/>
-      <c r="AY28" s="3"/>
-      <c r="AZ28" s="3"/>
-      <c r="BA28" s="3"/>
-      <c r="BB28" s="3"/>
-      <c r="BC28" s="3"/>
-      <c r="BD28" s="3"/>
-      <c r="BE28" s="3"/>
-      <c r="BF28" s="3"/>
-      <c r="BG28" s="3"/>
-      <c r="BH28" s="3"/>
-      <c r="BI28" s="3"/>
-      <c r="BJ28" s="3"/>
-      <c r="BK28" s="3"/>
-      <c r="BL28" s="3"/>
-      <c r="BM28" s="3"/>
-      <c r="BN28" s="3"/>
-      <c r="BO28" s="3"/>
-      <c r="BP28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BQ28" s="3"/>
-      <c r="BR28" s="3"/>
-    </row>
-    <row r="29" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="2" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>1</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1</v>
+      </c>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3">
+        <v>1</v>
+      </c>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3"/>
+      <c r="AJ30" s="3"/>
+      <c r="AK30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="3"/>
+      <c r="AN30" s="3"/>
+      <c r="AO30" s="3"/>
+      <c r="AP30" s="3"/>
+      <c r="AQ30" s="3"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT30" s="3"/>
+      <c r="AU30" s="3"/>
+      <c r="AV30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AW30" s="3"/>
+      <c r="AX30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY30" s="3"/>
+      <c r="AZ30" s="3"/>
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="3"/>
+      <c r="BC30" s="3"/>
+      <c r="BD30" s="3"/>
+      <c r="BE30" s="3"/>
+      <c r="BF30" s="3"/>
+      <c r="BG30" s="3"/>
+      <c r="BH30" s="3"/>
+      <c r="BI30" s="3"/>
+      <c r="BJ30" s="3"/>
+      <c r="BK30" s="3"/>
+      <c r="BL30" s="3"/>
+      <c r="BM30" s="3"/>
+      <c r="BN30" s="3"/>
+      <c r="BO30" s="3"/>
+      <c r="BP30" s="3"/>
+      <c r="BQ30" s="3"/>
+      <c r="BR30" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS30" s="3"/>
+      <c r="BT30" s="3"/>
+    </row>
+    <row r="31" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-      <c r="AD29" s="2"/>
-      <c r="AE29" s="2"/>
-      <c r="AF29" s="2"/>
-      <c r="AG29" s="2"/>
-      <c r="AH29" s="2"/>
-      <c r="AI29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ29" s="2"/>
-      <c r="AK29" s="2"/>
-      <c r="AL29" s="2"/>
-      <c r="AM29" s="2"/>
-      <c r="AN29" s="2"/>
-      <c r="AO29" s="2"/>
-      <c r="AP29" s="2"/>
-      <c r="AQ29" s="2"/>
-      <c r="AR29" s="2"/>
-      <c r="AS29" s="2"/>
-      <c r="AT29" s="2"/>
-      <c r="AU29" s="2"/>
-      <c r="AV29" s="2"/>
-      <c r="AW29" s="2"/>
-      <c r="AX29" s="2"/>
-      <c r="AY29" s="2"/>
-      <c r="AZ29" s="2"/>
-      <c r="BA29" s="2"/>
-      <c r="BB29" s="2"/>
-      <c r="BC29" s="2"/>
-      <c r="BD29" s="2"/>
-      <c r="BE29" s="2"/>
-      <c r="BF29" s="2"/>
-      <c r="BG29" s="2"/>
-      <c r="BH29" s="2"/>
-      <c r="BI29" s="2"/>
-      <c r="BJ29" s="2"/>
-      <c r="BK29" s="2"/>
-      <c r="BL29" s="2"/>
-      <c r="BM29" s="2"/>
-      <c r="BN29" s="2"/>
-      <c r="BO29" s="2"/>
-      <c r="BP29" s="2"/>
-      <c r="BQ29" s="2"/>
-      <c r="BR29" s="2"/>
-    </row>
-    <row r="30" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AH31" s="2"/>
+      <c r="AI31" s="2"/>
+      <c r="AJ31" s="2"/>
+      <c r="AK31" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="2"/>
+      <c r="AM31" s="2"/>
+      <c r="AN31" s="2"/>
+      <c r="AO31" s="2"/>
+      <c r="AP31" s="2"/>
+      <c r="AQ31" s="2"/>
+      <c r="AR31" s="2"/>
+      <c r="AS31" s="2"/>
+      <c r="AT31" s="2"/>
+      <c r="AU31" s="2"/>
+      <c r="AV31" s="2"/>
+      <c r="AW31" s="2"/>
+      <c r="AX31" s="2"/>
+      <c r="AY31" s="2"/>
+      <c r="AZ31" s="2"/>
+      <c r="BA31" s="2"/>
+      <c r="BB31" s="2"/>
+      <c r="BC31" s="2"/>
+      <c r="BD31" s="2"/>
+      <c r="BE31" s="2"/>
+      <c r="BF31" s="2"/>
+      <c r="BG31" s="2"/>
+      <c r="BH31" s="2"/>
+      <c r="BI31" s="2"/>
+      <c r="BJ31" s="2"/>
+      <c r="BK31" s="2"/>
+      <c r="BL31" s="2"/>
+      <c r="BM31" s="2"/>
+      <c r="BN31" s="2"/>
+      <c r="BO31" s="2"/>
+      <c r="BP31" s="2"/>
+      <c r="BQ31" s="2"/>
+      <c r="BR31" s="2"/>
+      <c r="BS31" s="2"/>
+      <c r="BT31" s="2"/>
+    </row>
+    <row r="32" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="2"/>
-      <c r="AA30" s="2"/>
-      <c r="AB30" s="2"/>
-      <c r="AC30" s="2"/>
-      <c r="AD30" s="2"/>
-      <c r="AE30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="2"/>
-      <c r="AG30" s="2"/>
-      <c r="AH30" s="2"/>
-      <c r="AI30" s="2"/>
-      <c r="AJ30" s="2"/>
-      <c r="AK30" s="2"/>
-      <c r="AL30" s="2"/>
-      <c r="AM30" s="2"/>
-      <c r="AN30" s="2"/>
-      <c r="AO30" s="2"/>
-      <c r="AP30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ30" s="2"/>
-      <c r="AR30" s="2"/>
-      <c r="AS30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT30" s="2"/>
-      <c r="AU30" s="2"/>
-      <c r="AV30" s="2"/>
-      <c r="AW30" s="2"/>
-      <c r="AX30" s="2"/>
-      <c r="AY30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ30" s="2"/>
-      <c r="BA30" s="2"/>
-      <c r="BB30" s="2"/>
-      <c r="BC30" s="2"/>
-      <c r="BD30" s="2"/>
-      <c r="BE30" s="2"/>
-      <c r="BF30" s="2"/>
-      <c r="BG30" s="2"/>
-      <c r="BH30" s="2"/>
-      <c r="BI30" s="2"/>
-      <c r="BJ30" s="2"/>
-      <c r="BK30" s="2"/>
-      <c r="BL30" s="2"/>
-      <c r="BM30" s="2"/>
-      <c r="BN30" s="2"/>
-      <c r="BO30" s="2"/>
-      <c r="BP30" s="2"/>
-      <c r="BQ30" s="2"/>
-      <c r="BR30" s="2"/>
-    </row>
-    <row r="31" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="2"/>
+      <c r="AG32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="2"/>
+      <c r="AI32" s="2"/>
+      <c r="AJ32" s="2"/>
+      <c r="AK32" s="2"/>
+      <c r="AL32" s="2"/>
+      <c r="AM32" s="2"/>
+      <c r="AN32" s="2"/>
+      <c r="AO32" s="2"/>
+      <c r="AP32" s="2"/>
+      <c r="AQ32" s="2"/>
+      <c r="AR32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="2"/>
+      <c r="AT32" s="2"/>
+      <c r="AU32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV32" s="2"/>
+      <c r="AW32" s="2"/>
+      <c r="AX32" s="2"/>
+      <c r="AY32" s="2"/>
+      <c r="AZ32" s="2"/>
+      <c r="BA32" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB32" s="2"/>
+      <c r="BC32" s="2"/>
+      <c r="BD32" s="2"/>
+      <c r="BE32" s="2"/>
+      <c r="BF32" s="2"/>
+      <c r="BG32" s="2"/>
+      <c r="BH32" s="2"/>
+      <c r="BI32" s="2"/>
+      <c r="BJ32" s="2"/>
+      <c r="BK32" s="2"/>
+      <c r="BL32" s="2"/>
+      <c r="BM32" s="2"/>
+      <c r="BN32" s="2"/>
+      <c r="BO32" s="2"/>
+      <c r="BP32" s="2"/>
+      <c r="BQ32" s="2"/>
+      <c r="BR32" s="2"/>
+      <c r="BS32" s="2"/>
+      <c r="BT32" s="2"/>
+    </row>
+    <row r="33" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
         <v>77</v>
       </c>
-      <c r="AC31">
-        <v>1</v>
-      </c>
-      <c r="AG31">
-        <v>1</v>
-      </c>
-      <c r="AH31">
-        <v>1</v>
-      </c>
-      <c r="AJ31">
-        <v>1</v>
-      </c>
-      <c r="AL31">
-        <v>1</v>
-      </c>
-      <c r="AM31">
-        <v>1</v>
-      </c>
-      <c r="AN31">
-        <v>1</v>
-      </c>
-      <c r="AO31">
-        <v>1</v>
-      </c>
-      <c r="AP31">
-        <v>1</v>
-      </c>
-      <c r="AQ31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
+      <c r="AE33">
+        <v>1</v>
+      </c>
+      <c r="AI33">
+        <v>1</v>
+      </c>
+      <c r="AJ33">
+        <v>1</v>
+      </c>
+      <c r="AL33">
+        <v>1</v>
+      </c>
+      <c r="AN33">
+        <v>1</v>
+      </c>
+      <c r="AO33">
+        <v>1</v>
+      </c>
+      <c r="AP33">
+        <v>1</v>
+      </c>
+      <c r="AQ33">
+        <v>1</v>
+      </c>
+      <c r="AR33">
+        <v>1</v>
+      </c>
+      <c r="AS33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
         <v>78</v>
       </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="AC32">
-        <v>1</v>
-      </c>
-      <c r="AJ32">
-        <v>1</v>
-      </c>
-      <c r="AQ32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+      <c r="AE34">
+        <v>1</v>
+      </c>
+      <c r="AL34">
+        <v>1</v>
+      </c>
+      <c r="AS34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="AC33">
-        <v>1</v>
-      </c>
-      <c r="AS33">
-        <v>1</v>
-      </c>
-      <c r="AY33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
+      <c r="AE35">
+        <v>1</v>
+      </c>
+      <c r="AU35">
+        <v>1</v>
+      </c>
+      <c r="BA35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
         <v>80</v>
       </c>
-      <c r="S34">
-        <v>1</v>
-      </c>
-      <c r="AC34">
-        <v>1</v>
-      </c>
-      <c r="AP34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A35" t="s">
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="AE36">
+        <v>1</v>
+      </c>
+      <c r="AR36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A36" s="2" t="s">
+    <row r="38" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2">
-        <v>1</v>
-      </c>
-      <c r="S36" s="2">
-        <v>1</v>
-      </c>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-      <c r="Y36" s="2"/>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2"/>
-      <c r="AB36" s="2"/>
-      <c r="AC36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE36" s="2"/>
-      <c r="AF36" s="2"/>
-      <c r="AG36" s="2"/>
-      <c r="AH36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ36" s="2"/>
-      <c r="AK36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AL36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AP36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ36" s="2"/>
-      <c r="AR36" s="2"/>
-      <c r="AS36" s="2"/>
-      <c r="AT36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX36" s="2"/>
-      <c r="AY36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ36" s="2">
-        <v>1</v>
-      </c>
-      <c r="BA36" s="2"/>
-      <c r="BB36" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC36" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD36" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE36" s="2"/>
-      <c r="BF36" s="2"/>
-      <c r="BG36" s="2"/>
-      <c r="BH36" s="2"/>
-      <c r="BI36" s="2"/>
-      <c r="BJ36" s="2"/>
-      <c r="BK36" s="2"/>
-      <c r="BL36" s="2"/>
-      <c r="BM36" s="2">
-        <v>1</v>
-      </c>
-      <c r="BN36" s="2"/>
-      <c r="BO36" s="2"/>
-      <c r="BP36" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ36" s="2"/>
-      <c r="BR36" s="2"/>
-    </row>
-    <row r="37" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2">
+        <v>1</v>
+      </c>
+      <c r="U38" s="2">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="2"/>
+      <c r="AH38" s="2"/>
+      <c r="AI38" s="2"/>
+      <c r="AJ38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL38" s="2"/>
+      <c r="AM38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS38" s="2"/>
+      <c r="AT38" s="2"/>
+      <c r="AU38" s="2"/>
+      <c r="AV38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AX38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ38" s="2"/>
+      <c r="BA38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BC38" s="2"/>
+      <c r="BD38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BE38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BG38" s="2"/>
+      <c r="BH38" s="2"/>
+      <c r="BI38" s="2"/>
+      <c r="BJ38" s="2"/>
+      <c r="BK38" s="2"/>
+      <c r="BL38" s="2"/>
+      <c r="BM38" s="2"/>
+      <c r="BN38" s="2"/>
+      <c r="BO38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BP38" s="2"/>
+      <c r="BQ38" s="2"/>
+      <c r="BR38" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS38" s="2"/>
+      <c r="BT38" s="2"/>
+    </row>
+    <row r="39" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="AC37">
-        <v>1</v>
-      </c>
-      <c r="AI37">
-        <v>1</v>
-      </c>
-      <c r="AV37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+      <c r="AE39">
+        <v>1</v>
+      </c>
+      <c r="AK39">
+        <v>1</v>
+      </c>
+      <c r="AX39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
         <v>5</v>
       </c>
-      <c r="R38">
-        <v>1</v>
-      </c>
-      <c r="S38">
-        <v>1</v>
-      </c>
-      <c r="AC38">
-        <v>1</v>
-      </c>
-      <c r="AM38">
-        <v>1</v>
-      </c>
-      <c r="AN38">
-        <v>1</v>
-      </c>
-      <c r="AO38">
-        <v>1</v>
-      </c>
-      <c r="AP38">
-        <v>1</v>
-      </c>
-      <c r="AW38">
-        <v>1</v>
-      </c>
-      <c r="AY38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="3" t="s">
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="AE40">
+        <v>1</v>
+      </c>
+      <c r="AO40">
+        <v>1</v>
+      </c>
+      <c r="AP40">
+        <v>1</v>
+      </c>
+      <c r="AQ40">
+        <v>1</v>
+      </c>
+      <c r="AR40">
+        <v>1</v>
+      </c>
+      <c r="AY40">
+        <v>1</v>
+      </c>
+      <c r="BA40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
-      <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="3"/>
-      <c r="AG39" s="3"/>
-      <c r="AH39" s="3"/>
-      <c r="AI39" s="3"/>
-      <c r="AJ39" s="3"/>
-      <c r="AK39" s="3"/>
-      <c r="AL39" s="3"/>
-      <c r="AM39" s="3"/>
-      <c r="AN39" s="3"/>
-      <c r="AO39" s="3"/>
-      <c r="AP39" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ39" s="3"/>
-      <c r="AR39" s="3"/>
-      <c r="AS39" s="3"/>
-      <c r="AT39" s="3"/>
-      <c r="AU39" s="3"/>
-      <c r="AV39" s="3"/>
-      <c r="AW39" s="3"/>
-      <c r="AX39" s="3"/>
-      <c r="AY39" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ39" s="3"/>
-      <c r="BA39" s="3"/>
-      <c r="BB39" s="3"/>
-      <c r="BC39" s="3"/>
-      <c r="BD39" s="3"/>
-      <c r="BE39" s="3"/>
-      <c r="BF39" s="3"/>
-      <c r="BG39" s="3"/>
-      <c r="BH39" s="3"/>
-      <c r="BI39" s="3"/>
-      <c r="BJ39" s="3"/>
-      <c r="BK39" s="3"/>
-      <c r="BL39" s="3"/>
-      <c r="BM39" s="3"/>
-      <c r="BN39" s="3"/>
-      <c r="BO39" s="3"/>
-      <c r="BP39" s="3"/>
-      <c r="BQ39" s="3"/>
-      <c r="BR39" s="3"/>
-    </row>
-    <row r="40" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A40" s="1" t="s">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+      <c r="AH41" s="3"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="3"/>
+      <c r="AK41" s="3"/>
+      <c r="AL41" s="3"/>
+      <c r="AM41" s="3"/>
+      <c r="AN41" s="3"/>
+      <c r="AO41" s="3"/>
+      <c r="AP41" s="3"/>
+      <c r="AQ41" s="3"/>
+      <c r="AR41" s="3">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="3"/>
+      <c r="AT41" s="3"/>
+      <c r="AU41" s="3"/>
+      <c r="AV41" s="3"/>
+      <c r="AW41" s="3"/>
+      <c r="AX41" s="3"/>
+      <c r="AY41" s="3"/>
+      <c r="AZ41" s="3"/>
+      <c r="BA41" s="3">
+        <v>1</v>
+      </c>
+      <c r="BB41" s="3"/>
+      <c r="BC41" s="3"/>
+      <c r="BD41" s="3"/>
+      <c r="BE41" s="3"/>
+      <c r="BF41" s="3"/>
+      <c r="BG41" s="3"/>
+      <c r="BH41" s="3"/>
+      <c r="BI41" s="3"/>
+      <c r="BJ41" s="3"/>
+      <c r="BK41" s="3"/>
+      <c r="BL41" s="3"/>
+      <c r="BM41" s="3"/>
+      <c r="BN41" s="3"/>
+      <c r="BO41" s="3"/>
+      <c r="BP41" s="3"/>
+      <c r="BQ41" s="3"/>
+      <c r="BR41" s="3"/>
+      <c r="BS41" s="3"/>
+      <c r="BT41" s="3"/>
+    </row>
+    <row r="42" spans="1:72" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AP40">
-        <v>1</v>
-      </c>
-      <c r="AY40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="AR42">
+        <v>1</v>
+      </c>
+      <c r="BA42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
         <v>6</v>
       </c>
-      <c r="AP41">
-        <v>1</v>
-      </c>
-      <c r="AY41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A42" t="s">
+      <c r="AR43">
+        <v>1</v>
+      </c>
+      <c r="BA43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A44" t="s">
         <v>25</v>
       </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="AC42">
-        <v>1</v>
-      </c>
-      <c r="AI42">
-        <v>1</v>
-      </c>
-      <c r="AY42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="5" t="s">
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="AE44">
+        <v>1</v>
+      </c>
+      <c r="AK44">
+        <v>1</v>
+      </c>
+      <c r="BA44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A45" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5">
-        <v>1</v>
-      </c>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="5"/>
-      <c r="W43" s="5"/>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="5"/>
-      <c r="AA43" s="5"/>
-      <c r="AB43" s="5"/>
-      <c r="AC43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AE43" s="5"/>
-      <c r="AF43" s="5"/>
-      <c r="AG43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AH43" s="5"/>
-      <c r="AI43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AJ43" s="5"/>
-      <c r="AK43" s="5"/>
-      <c r="AL43" s="5"/>
-      <c r="AM43" s="5"/>
-      <c r="AN43" s="5"/>
-      <c r="AO43" s="5"/>
-      <c r="AP43" s="5"/>
-      <c r="AQ43" s="5"/>
-      <c r="AR43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AT43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AU43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AV43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AW43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AX43" s="5"/>
-      <c r="AY43" s="5">
-        <v>1</v>
-      </c>
-      <c r="AZ43" s="5">
-        <v>1</v>
-      </c>
-      <c r="BA43" s="5"/>
-      <c r="BB43" s="5">
-        <v>1</v>
-      </c>
-      <c r="BC43" s="5">
-        <v>1</v>
-      </c>
-      <c r="BD43" s="5">
-        <v>1</v>
-      </c>
-      <c r="BE43" s="5"/>
-      <c r="BF43" s="5"/>
-      <c r="BG43" s="5"/>
-      <c r="BH43" s="5"/>
-      <c r="BI43" s="5"/>
-      <c r="BJ43" s="5"/>
-      <c r="BK43" s="5"/>
-      <c r="BL43" s="5"/>
-      <c r="BM43" s="5">
-        <v>1</v>
-      </c>
-      <c r="BN43" s="5"/>
-      <c r="BO43" s="5">
-        <v>1</v>
-      </c>
-      <c r="BP43" s="5"/>
-      <c r="BQ43" s="5"/>
-      <c r="BR43" s="5"/>
-    </row>
-    <row r="44" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="3" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5">
+        <v>1</v>
+      </c>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="5"/>
+      <c r="AB45" s="5"/>
+      <c r="AC45" s="5"/>
+      <c r="AD45" s="5"/>
+      <c r="AE45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="5"/>
+      <c r="AH45" s="5"/>
+      <c r="AI45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AJ45" s="5"/>
+      <c r="AK45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AL45" s="5"/>
+      <c r="AM45" s="5"/>
+      <c r="AN45" s="5"/>
+      <c r="AO45" s="5"/>
+      <c r="AP45" s="5"/>
+      <c r="AQ45" s="5"/>
+      <c r="AR45" s="5"/>
+      <c r="AS45" s="5"/>
+      <c r="AT45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AU45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AW45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AX45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AY45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC45" s="5"/>
+      <c r="BD45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BE45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BG45" s="5"/>
+      <c r="BH45" s="5"/>
+      <c r="BI45" s="5"/>
+      <c r="BJ45" s="5"/>
+      <c r="BK45" s="5"/>
+      <c r="BL45" s="5"/>
+      <c r="BM45" s="5"/>
+      <c r="BN45" s="5"/>
+      <c r="BO45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BP45" s="5"/>
+      <c r="BQ45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BR45" s="5"/>
+      <c r="BS45" s="5"/>
+      <c r="BT45" s="5"/>
+    </row>
+    <row r="46" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
-      <c r="AB44" s="3"/>
-      <c r="AC44" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD44" s="3"/>
-      <c r="AE44" s="3"/>
-      <c r="AF44" s="3"/>
-      <c r="AG44" s="3"/>
-      <c r="AH44" s="3"/>
-      <c r="AI44" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ44" s="3"/>
-      <c r="AK44" s="3"/>
-      <c r="AL44" s="3"/>
-      <c r="AM44" s="3"/>
-      <c r="AN44" s="3"/>
-      <c r="AO44" s="3"/>
-      <c r="AP44" s="3"/>
-      <c r="AQ44" s="3"/>
-      <c r="AR44" s="3"/>
-      <c r="AS44" s="3"/>
-      <c r="AT44" s="3"/>
-      <c r="AU44" s="3"/>
-      <c r="AV44" s="3">
-        <v>1</v>
-      </c>
-      <c r="AW44" s="3"/>
-      <c r="AX44" s="3"/>
-      <c r="AY44" s="3"/>
-      <c r="AZ44" s="3"/>
-      <c r="BA44" s="3"/>
-      <c r="BB44" s="3"/>
-      <c r="BC44" s="3"/>
-      <c r="BD44" s="3"/>
-      <c r="BE44" s="3"/>
-      <c r="BF44" s="3"/>
-      <c r="BG44" s="3"/>
-      <c r="BH44" s="3"/>
-      <c r="BI44" s="3"/>
-      <c r="BJ44" s="3"/>
-      <c r="BK44" s="3"/>
-      <c r="BL44" s="3"/>
-      <c r="BM44" s="3"/>
-      <c r="BN44" s="3"/>
-      <c r="BO44" s="3"/>
-      <c r="BP44" s="3"/>
-      <c r="BQ44" s="3"/>
-      <c r="BR44" s="3"/>
-    </row>
-    <row r="45" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A45" s="2" t="s">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
+      <c r="AC46" s="3"/>
+      <c r="AD46" s="3"/>
+      <c r="AE46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="3"/>
+      <c r="AG46" s="3"/>
+      <c r="AH46" s="3"/>
+      <c r="AI46" s="3"/>
+      <c r="AJ46" s="3"/>
+      <c r="AK46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL46" s="3"/>
+      <c r="AM46" s="3"/>
+      <c r="AN46" s="3"/>
+      <c r="AO46" s="3"/>
+      <c r="AP46" s="3"/>
+      <c r="AQ46" s="3"/>
+      <c r="AR46" s="3"/>
+      <c r="AS46" s="3"/>
+      <c r="AT46" s="3"/>
+      <c r="AU46" s="3"/>
+      <c r="AV46" s="3"/>
+      <c r="AW46" s="3"/>
+      <c r="AX46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY46" s="3"/>
+      <c r="AZ46" s="3"/>
+      <c r="BA46" s="3"/>
+      <c r="BB46" s="3"/>
+      <c r="BC46" s="3"/>
+      <c r="BD46" s="3"/>
+      <c r="BE46" s="3"/>
+      <c r="BF46" s="3"/>
+      <c r="BG46" s="3"/>
+      <c r="BH46" s="3"/>
+      <c r="BI46" s="3"/>
+      <c r="BJ46" s="3"/>
+      <c r="BK46" s="3"/>
+      <c r="BL46" s="3"/>
+      <c r="BM46" s="3"/>
+      <c r="BN46" s="3"/>
+      <c r="BO46" s="3"/>
+      <c r="BP46" s="3"/>
+      <c r="BQ46" s="3"/>
+      <c r="BR46" s="3"/>
+      <c r="BS46" s="3"/>
+      <c r="BT46" s="3"/>
+    </row>
+    <row r="47" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="2">
-        <v>1</v>
-      </c>
-      <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="2"/>
-      <c r="X45" s="2"/>
-      <c r="Y45" s="2"/>
-      <c r="Z45" s="2"/>
-      <c r="AA45" s="2"/>
-      <c r="AB45" s="2"/>
-      <c r="AC45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD45" s="2"/>
-      <c r="AE45" s="2"/>
-      <c r="AF45" s="2"/>
-      <c r="AG45" s="2"/>
-      <c r="AH45" s="2"/>
-      <c r="AI45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ45" s="2"/>
-      <c r="AK45" s="2"/>
-      <c r="AL45" s="2"/>
-      <c r="AM45" s="2"/>
-      <c r="AN45" s="2"/>
-      <c r="AO45" s="2"/>
-      <c r="AP45" s="2"/>
-      <c r="AQ45" s="2"/>
-      <c r="AR45" s="2"/>
-      <c r="AS45" s="2"/>
-      <c r="AT45" s="2"/>
-      <c r="AU45" s="2"/>
-      <c r="AV45" s="2"/>
-      <c r="AW45" s="2"/>
-      <c r="AX45" s="2"/>
-      <c r="AY45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ45" s="2"/>
-      <c r="BA45" s="2"/>
-      <c r="BB45" s="2"/>
-      <c r="BC45" s="2"/>
-      <c r="BD45" s="2"/>
-      <c r="BE45" s="2"/>
-      <c r="BF45" s="2"/>
-      <c r="BG45" s="2"/>
-      <c r="BH45" s="2"/>
-      <c r="BI45" s="2"/>
-      <c r="BJ45" s="2"/>
-      <c r="BK45" s="2"/>
-      <c r="BL45" s="2"/>
-      <c r="BM45" s="2"/>
-      <c r="BN45" s="2"/>
-      <c r="BO45" s="2"/>
-      <c r="BP45" s="2"/>
-      <c r="BQ45" s="2"/>
-      <c r="BR45" s="2"/>
-    </row>
-    <row r="46" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="2"/>
+      <c r="AE47" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="2"/>
+      <c r="AG47" s="2"/>
+      <c r="AH47" s="2"/>
+      <c r="AI47" s="2"/>
+      <c r="AJ47" s="2"/>
+      <c r="AK47" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL47" s="2"/>
+      <c r="AM47" s="2"/>
+      <c r="AN47" s="2"/>
+      <c r="AO47" s="2"/>
+      <c r="AP47" s="2"/>
+      <c r="AQ47" s="2"/>
+      <c r="AR47" s="2"/>
+      <c r="AS47" s="2"/>
+      <c r="AT47" s="2"/>
+      <c r="AU47" s="2"/>
+      <c r="AV47" s="2"/>
+      <c r="AW47" s="2"/>
+      <c r="AX47" s="2"/>
+      <c r="AY47" s="2"/>
+      <c r="AZ47" s="2"/>
+      <c r="BA47" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB47" s="2"/>
+      <c r="BC47" s="2"/>
+      <c r="BD47" s="2"/>
+      <c r="BE47" s="2"/>
+      <c r="BF47" s="2"/>
+      <c r="BG47" s="2"/>
+      <c r="BH47" s="2"/>
+      <c r="BI47" s="2"/>
+      <c r="BJ47" s="2"/>
+      <c r="BK47" s="2"/>
+      <c r="BL47" s="2"/>
+      <c r="BM47" s="2"/>
+      <c r="BN47" s="2"/>
+      <c r="BO47" s="2"/>
+      <c r="BP47" s="2"/>
+      <c r="BQ47" s="2"/>
+      <c r="BR47" s="2"/>
+      <c r="BS47" s="2"/>
+      <c r="BT47" s="2"/>
+    </row>
+    <row r="48" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A48" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2">
-        <v>1</v>
-      </c>
-      <c r="S46" s="2">
-        <v>1</v>
-      </c>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD46" s="2"/>
-      <c r="AE46" s="2"/>
-      <c r="AF46" s="2"/>
-      <c r="AG46" s="2"/>
-      <c r="AH46" s="2"/>
-      <c r="AI46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ46" s="2"/>
-      <c r="AK46" s="2"/>
-      <c r="AL46" s="2"/>
-      <c r="AM46" s="2"/>
-      <c r="AN46" s="2"/>
-      <c r="AO46" s="2"/>
-      <c r="AP46" s="2"/>
-      <c r="AQ46" s="2"/>
-      <c r="AR46" s="2"/>
-      <c r="AS46" s="2"/>
-      <c r="AT46" s="2"/>
-      <c r="AU46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV46" s="2"/>
-      <c r="AW46" s="2"/>
-      <c r="AX46" s="2"/>
-      <c r="AY46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ46" s="2"/>
-      <c r="BA46" s="2"/>
-      <c r="BB46" s="2"/>
-      <c r="BC46" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD46" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE46" s="2"/>
-      <c r="BF46" s="2"/>
-      <c r="BG46" s="2"/>
-      <c r="BH46" s="2"/>
-      <c r="BI46" s="2"/>
-      <c r="BJ46" s="2"/>
-      <c r="BK46" s="2"/>
-      <c r="BL46" s="2"/>
-      <c r="BM46" s="2">
-        <v>1</v>
-      </c>
-      <c r="BN46" s="2"/>
-      <c r="BO46" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP46" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ46" s="2"/>
-      <c r="BR46" s="2"/>
-    </row>
-    <row r="47" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
-      <c r="AB47" s="3"/>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3"/>
-      <c r="AG47" s="3"/>
-      <c r="AH47" s="3"/>
-      <c r="AI47" s="3"/>
-      <c r="AJ47" s="3"/>
-      <c r="AK47" s="3"/>
-      <c r="AL47" s="3"/>
-      <c r="AM47" s="3"/>
-      <c r="AN47" s="3"/>
-      <c r="AO47" s="3"/>
-      <c r="AP47" s="3"/>
-      <c r="AQ47" s="3"/>
-      <c r="AR47" s="3"/>
-      <c r="AS47" s="3"/>
-      <c r="AT47" s="3"/>
-      <c r="AU47" s="3"/>
-      <c r="AV47" s="3"/>
-      <c r="AW47" s="3"/>
-      <c r="AX47" s="3"/>
-      <c r="AY47" s="3"/>
-      <c r="AZ47" s="3"/>
-      <c r="BA47" s="3"/>
-      <c r="BB47" s="3"/>
-      <c r="BC47" s="3"/>
-      <c r="BD47" s="3"/>
-      <c r="BE47" s="3"/>
-      <c r="BF47" s="3"/>
-      <c r="BG47" s="3"/>
-      <c r="BH47" s="3"/>
-      <c r="BI47" s="3"/>
-      <c r="BJ47" s="3"/>
-      <c r="BK47" s="3"/>
-      <c r="BL47" s="3"/>
-      <c r="BM47" s="3"/>
-      <c r="BN47" s="3"/>
-      <c r="BO47" s="3"/>
-      <c r="BP47" s="3"/>
-      <c r="BQ47" s="3"/>
-      <c r="BR47" s="3"/>
-    </row>
-    <row r="48" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A48" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3850,14 +3925,14 @@
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
-      <c r="R48" s="2">
-        <v>1</v>
-      </c>
-      <c r="S48" s="2">
-        <v>1</v>
-      </c>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2">
+        <v>1</v>
+      </c>
+      <c r="U48" s="2">
+        <v>1</v>
+      </c>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
@@ -3865,19 +3940,19 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
       <c r="AB48" s="2"/>
-      <c r="AC48" s="2">
-        <v>1</v>
-      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" s="2"/>
-      <c r="AE48" s="2"/>
+      <c r="AE48" s="2">
+        <v>1</v>
+      </c>
       <c r="AF48" s="2"/>
       <c r="AG48" s="2"/>
       <c r="AH48" s="2"/>
-      <c r="AI48" s="2">
-        <v>1</v>
-      </c>
+      <c r="AI48" s="2"/>
       <c r="AJ48" s="2"/>
-      <c r="AK48" s="2"/>
+      <c r="AK48" s="2">
+        <v>1</v>
+      </c>
       <c r="AL48" s="2"/>
       <c r="AM48" s="2"/>
       <c r="AN48" s="2"/>
@@ -3892,542 +3967,645 @@
       <c r="AW48" s="2">
         <v>1</v>
       </c>
-      <c r="AX48" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY48" s="2">
-        <v>1</v>
-      </c>
+      <c r="AX48" s="2"/>
+      <c r="AY48" s="2"/>
       <c r="AZ48" s="2"/>
-      <c r="BA48" s="2"/>
+      <c r="BA48" s="2">
+        <v>1</v>
+      </c>
       <c r="BB48" s="2"/>
-      <c r="BC48" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD48" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE48" s="2"/>
-      <c r="BF48" s="2"/>
+      <c r="BC48" s="2"/>
+      <c r="BD48" s="2"/>
+      <c r="BE48" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF48" s="2">
+        <v>1</v>
+      </c>
       <c r="BG48" s="2"/>
       <c r="BH48" s="2"/>
       <c r="BI48" s="2"/>
       <c r="BJ48" s="2"/>
       <c r="BK48" s="2"/>
       <c r="BL48" s="2"/>
-      <c r="BM48" s="2">
-        <v>1</v>
-      </c>
+      <c r="BM48" s="2"/>
       <c r="BN48" s="2"/>
       <c r="BO48" s="2">
         <v>1</v>
       </c>
-      <c r="BP48" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ48" s="2"/>
-      <c r="BR48" s="2"/>
-    </row>
-    <row r="49" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
+      <c r="BP48" s="2"/>
+      <c r="BQ48" s="2">
+        <v>1</v>
+      </c>
+      <c r="BR48" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS48" s="2"/>
+      <c r="BT48" s="2"/>
+    </row>
+    <row r="49" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3"/>
+      <c r="AC49" s="3"/>
+      <c r="AD49" s="3"/>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
+      <c r="AH49" s="3"/>
+      <c r="AI49" s="3"/>
+      <c r="AJ49" s="3"/>
+      <c r="AK49" s="3"/>
+      <c r="AL49" s="3"/>
+      <c r="AM49" s="3"/>
+      <c r="AN49" s="3"/>
+      <c r="AO49" s="3"/>
+      <c r="AP49" s="3"/>
+      <c r="AQ49" s="3"/>
+      <c r="AR49" s="3"/>
+      <c r="AS49" s="3"/>
+      <c r="AT49" s="3"/>
+      <c r="AU49" s="3"/>
+      <c r="AV49" s="3"/>
+      <c r="AW49" s="3"/>
+      <c r="AX49" s="3"/>
+      <c r="AY49" s="3"/>
+      <c r="AZ49" s="3"/>
+      <c r="BA49" s="3"/>
+      <c r="BB49" s="3"/>
+      <c r="BC49" s="3"/>
+      <c r="BD49" s="3"/>
+      <c r="BE49" s="3"/>
+      <c r="BF49" s="3"/>
+      <c r="BG49" s="3"/>
+      <c r="BH49" s="3"/>
+      <c r="BI49" s="3"/>
+      <c r="BJ49" s="3"/>
+      <c r="BK49" s="3"/>
+      <c r="BL49" s="3"/>
+      <c r="BM49" s="3"/>
+      <c r="BN49" s="3"/>
+      <c r="BO49" s="3"/>
+      <c r="BP49" s="3"/>
+      <c r="BQ49" s="3"/>
+      <c r="BR49" s="3"/>
+      <c r="BS49" s="3"/>
+      <c r="BT49" s="3"/>
+    </row>
+    <row r="50" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2">
+        <v>1</v>
+      </c>
+      <c r="U50" s="2">
+        <v>1</v>
+      </c>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="2"/>
+      <c r="AE50" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="2"/>
+      <c r="AG50" s="2"/>
+      <c r="AH50" s="2"/>
+      <c r="AI50" s="2"/>
+      <c r="AJ50" s="2"/>
+      <c r="AK50" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL50" s="2"/>
+      <c r="AM50" s="2"/>
+      <c r="AN50" s="2"/>
+      <c r="AO50" s="2"/>
+      <c r="AP50" s="2"/>
+      <c r="AQ50" s="2"/>
+      <c r="AR50" s="2"/>
+      <c r="AS50" s="2"/>
+      <c r="AT50" s="2"/>
+      <c r="AU50" s="2"/>
+      <c r="AV50" s="2"/>
+      <c r="AW50" s="2"/>
+      <c r="AX50" s="2"/>
+      <c r="AY50" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB50" s="2"/>
+      <c r="BC50" s="2"/>
+      <c r="BD50" s="2"/>
+      <c r="BE50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BG50" s="2"/>
+      <c r="BH50" s="2"/>
+      <c r="BI50" s="2"/>
+      <c r="BJ50" s="2"/>
+      <c r="BK50" s="2"/>
+      <c r="BL50" s="2"/>
+      <c r="BM50" s="2"/>
+      <c r="BN50" s="2"/>
+      <c r="BO50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BP50" s="2"/>
+      <c r="BQ50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BR50" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS50" s="2"/>
+      <c r="BT50" s="2"/>
+    </row>
+    <row r="51" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
         <v>15</v>
       </c>
-      <c r="S49">
-        <v>1</v>
-      </c>
-      <c r="AC49">
-        <v>1</v>
-      </c>
-      <c r="AY49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="AE51">
+        <v>1</v>
+      </c>
+      <c r="BA51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
         <v>70</v>
       </c>
-      <c r="AC50">
-        <v>1</v>
-      </c>
-      <c r="AI50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A51" s="3" t="s">
+      <c r="AE52">
+        <v>1</v>
+      </c>
+      <c r="AK52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A53" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3">
-        <v>1</v>
-      </c>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
-      <c r="AB51" s="3"/>
-      <c r="AC51" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD51" s="3"/>
-      <c r="AE51" s="3"/>
-      <c r="AF51" s="3"/>
-      <c r="AG51" s="3"/>
-      <c r="AH51" s="3"/>
-      <c r="AI51" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ51" s="3"/>
-      <c r="AK51" s="3"/>
-      <c r="AL51" s="3"/>
-      <c r="AM51" s="3"/>
-      <c r="AN51" s="3"/>
-      <c r="AO51" s="3"/>
-      <c r="AP51" s="3"/>
-      <c r="AQ51" s="3"/>
-      <c r="AR51" s="3"/>
-      <c r="AS51" s="3"/>
-      <c r="AT51" s="3"/>
-      <c r="AU51" s="3"/>
-      <c r="AV51" s="3"/>
-      <c r="AW51" s="3"/>
-      <c r="AX51" s="3"/>
-      <c r="AY51" s="3"/>
-      <c r="AZ51" s="3"/>
-      <c r="BA51" s="3"/>
-      <c r="BB51" s="3"/>
-      <c r="BC51" s="3"/>
-      <c r="BD51" s="3"/>
-      <c r="BE51" s="3"/>
-      <c r="BF51" s="3"/>
-      <c r="BG51" s="3"/>
-      <c r="BH51" s="3"/>
-      <c r="BI51" s="3"/>
-      <c r="BJ51" s="3"/>
-      <c r="BK51" s="3"/>
-      <c r="BL51" s="3"/>
-      <c r="BM51" s="3"/>
-      <c r="BN51" s="3"/>
-      <c r="BO51" s="3"/>
-      <c r="BP51" s="3"/>
-      <c r="BQ51" s="3"/>
-      <c r="BR51" s="3"/>
-    </row>
-    <row r="52" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A52" s="2" t="s">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3">
+        <v>1</v>
+      </c>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="3"/>
+      <c r="AC53" s="3"/>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="3"/>
+      <c r="AG53" s="3"/>
+      <c r="AH53" s="3"/>
+      <c r="AI53" s="3"/>
+      <c r="AJ53" s="3"/>
+      <c r="AK53" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL53" s="3"/>
+      <c r="AM53" s="3"/>
+      <c r="AN53" s="3"/>
+      <c r="AO53" s="3"/>
+      <c r="AP53" s="3"/>
+      <c r="AQ53" s="3"/>
+      <c r="AR53" s="3"/>
+      <c r="AS53" s="3"/>
+      <c r="AT53" s="3"/>
+      <c r="AU53" s="3"/>
+      <c r="AV53" s="3"/>
+      <c r="AW53" s="3"/>
+      <c r="AX53" s="3"/>
+      <c r="AY53" s="3"/>
+      <c r="AZ53" s="3"/>
+      <c r="BA53" s="3"/>
+      <c r="BB53" s="3"/>
+      <c r="BC53" s="3"/>
+      <c r="BD53" s="3"/>
+      <c r="BE53" s="3"/>
+      <c r="BF53" s="3"/>
+      <c r="BG53" s="3"/>
+      <c r="BH53" s="3"/>
+      <c r="BI53" s="3"/>
+      <c r="BJ53" s="3"/>
+      <c r="BK53" s="3"/>
+      <c r="BL53" s="3"/>
+      <c r="BM53" s="3"/>
+      <c r="BN53" s="3"/>
+      <c r="BO53" s="3"/>
+      <c r="BP53" s="3"/>
+      <c r="BQ53" s="3"/>
+      <c r="BR53" s="3"/>
+      <c r="BS53" s="3"/>
+      <c r="BT53" s="3"/>
+    </row>
+    <row r="54" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2">
-        <v>1</v>
-      </c>
-      <c r="P52" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="2"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="2"/>
-      <c r="X52" s="2"/>
-      <c r="Y52" s="2"/>
-      <c r="Z52" s="2"/>
-      <c r="AA52" s="2"/>
-      <c r="AB52" s="2"/>
-      <c r="AC52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD52" s="2"/>
-      <c r="AE52" s="2"/>
-      <c r="AF52" s="2"/>
-      <c r="AG52" s="2"/>
-      <c r="AH52" s="2"/>
-      <c r="AI52" s="2"/>
-      <c r="AJ52" s="2"/>
-      <c r="AK52" s="2"/>
-      <c r="AL52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO52" s="2"/>
-      <c r="AP52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ52" s="2"/>
-      <c r="AR52" s="2"/>
-      <c r="AS52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT52" s="2"/>
-      <c r="AU52" s="2"/>
-      <c r="AV52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW52" s="2"/>
-      <c r="AX52" s="2"/>
-      <c r="AY52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ52" s="2"/>
-      <c r="BA52" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB52" s="2"/>
-      <c r="BC52" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD52" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE52" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF52" s="2"/>
-      <c r="BG52" s="2"/>
-      <c r="BH52" s="2"/>
-      <c r="BI52" s="2"/>
-      <c r="BJ52" s="2"/>
-      <c r="BK52" s="2"/>
-      <c r="BL52" s="2"/>
-      <c r="BM52" s="2"/>
-      <c r="BN52" s="2"/>
-      <c r="BO52" s="2"/>
-      <c r="BP52" s="2"/>
-      <c r="BQ52" s="2"/>
-      <c r="BR52" s="2"/>
-    </row>
-    <row r="53" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2">
+        <v>1</v>
+      </c>
+      <c r="R54" s="2">
+        <v>1</v>
+      </c>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2"/>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2"/>
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="2"/>
+      <c r="AE54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="2"/>
+      <c r="AG54" s="2"/>
+      <c r="AH54" s="2"/>
+      <c r="AI54" s="2"/>
+      <c r="AJ54" s="2"/>
+      <c r="AK54" s="2"/>
+      <c r="AL54" s="2"/>
+      <c r="AM54" s="2"/>
+      <c r="AN54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ54" s="2"/>
+      <c r="AR54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS54" s="2"/>
+      <c r="AT54" s="2"/>
+      <c r="AU54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV54" s="2"/>
+      <c r="AW54" s="2"/>
+      <c r="AX54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY54" s="2"/>
+      <c r="AZ54" s="2"/>
+      <c r="BA54" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB54" s="2"/>
+      <c r="BC54" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD54" s="2"/>
+      <c r="BE54" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF54" s="2">
+        <v>1</v>
+      </c>
+      <c r="BG54" s="2">
+        <v>1</v>
+      </c>
+      <c r="BH54" s="2"/>
+      <c r="BI54" s="2"/>
+      <c r="BJ54" s="2"/>
+      <c r="BK54" s="2"/>
+      <c r="BL54" s="2"/>
+      <c r="BM54" s="2"/>
+      <c r="BN54" s="2"/>
+      <c r="BO54" s="2"/>
+      <c r="BP54" s="2"/>
+      <c r="BQ54" s="2"/>
+      <c r="BR54" s="2"/>
+      <c r="BS54" s="2"/>
+      <c r="BT54" s="2"/>
+    </row>
+    <row r="55" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
         <v>42</v>
       </c>
-      <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="Z53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A54" t="s">
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="AB55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A56" t="s">
         <v>19</v>
       </c>
-      <c r="AC54">
-        <v>1</v>
-      </c>
-      <c r="AL54">
-        <v>1</v>
-      </c>
-      <c r="AM54">
-        <v>1</v>
-      </c>
-      <c r="AN54">
-        <v>1</v>
-      </c>
-      <c r="AP54">
-        <v>1</v>
-      </c>
-      <c r="AS54">
-        <v>1</v>
-      </c>
-      <c r="AV54">
-        <v>1</v>
-      </c>
-      <c r="AY54">
-        <v>1</v>
-      </c>
-      <c r="AZ54">
-        <v>1</v>
-      </c>
-      <c r="BA54">
-        <v>1</v>
-      </c>
-      <c r="BC54">
-        <v>1</v>
-      </c>
-      <c r="BD54">
-        <v>1</v>
-      </c>
-      <c r="BE54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A55" s="2" t="s">
+      <c r="AE56">
+        <v>1</v>
+      </c>
+      <c r="AN56">
+        <v>1</v>
+      </c>
+      <c r="AO56">
+        <v>1</v>
+      </c>
+      <c r="AP56">
+        <v>1</v>
+      </c>
+      <c r="AR56">
+        <v>1</v>
+      </c>
+      <c r="AU56">
+        <v>1</v>
+      </c>
+      <c r="AX56">
+        <v>1</v>
+      </c>
+      <c r="BA56">
+        <v>1</v>
+      </c>
+      <c r="BB56">
+        <v>1</v>
+      </c>
+      <c r="BC56">
+        <v>1</v>
+      </c>
+      <c r="BE56">
+        <v>1</v>
+      </c>
+      <c r="BF56">
+        <v>1</v>
+      </c>
+      <c r="BG56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-      <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
-      <c r="Y55" s="2"/>
-      <c r="Z55" s="2"/>
-      <c r="AA55" s="2"/>
-      <c r="AB55" s="2"/>
-      <c r="AC55" s="2"/>
-      <c r="AD55" s="2"/>
-      <c r="AE55" s="2"/>
-      <c r="AF55" s="2"/>
-      <c r="AG55" s="2"/>
-      <c r="AH55" s="2"/>
-      <c r="AI55" s="2"/>
-      <c r="AJ55" s="2"/>
-      <c r="AK55" s="2"/>
-      <c r="AL55" s="2"/>
-      <c r="AM55" s="2"/>
-      <c r="AN55" s="2"/>
-      <c r="AO55" s="2"/>
-      <c r="AP55" s="2"/>
-      <c r="AQ55" s="2"/>
-      <c r="AR55" s="2"/>
-      <c r="AS55" s="2"/>
-      <c r="AT55" s="2"/>
-      <c r="AU55" s="2"/>
-      <c r="AV55" s="2"/>
-      <c r="AW55" s="2"/>
-      <c r="AX55" s="2"/>
-      <c r="AY55" s="2"/>
-      <c r="AZ55" s="2"/>
-      <c r="BA55" s="2"/>
-      <c r="BB55" s="2"/>
-      <c r="BC55" s="2"/>
-      <c r="BD55" s="2"/>
-      <c r="BE55" s="2"/>
-      <c r="BF55" s="2"/>
-      <c r="BG55" s="2"/>
-      <c r="BH55" s="2"/>
-      <c r="BI55" s="2"/>
-      <c r="BJ55" s="2"/>
-      <c r="BK55" s="2"/>
-      <c r="BL55" s="2"/>
-      <c r="BM55" s="2"/>
-      <c r="BN55" s="2"/>
-      <c r="BO55" s="2"/>
-      <c r="BP55" s="2"/>
-      <c r="BQ55" s="2"/>
-      <c r="BR55" s="2"/>
-    </row>
-    <row r="56" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A56" s="2" t="s">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2"/>
+      <c r="W57" s="2"/>
+      <c r="X57" s="2"/>
+      <c r="Y57" s="2"/>
+      <c r="Z57" s="2"/>
+      <c r="AA57" s="2"/>
+      <c r="AB57" s="2"/>
+      <c r="AC57" s="2"/>
+      <c r="AD57" s="2"/>
+      <c r="AE57" s="2"/>
+      <c r="AF57" s="2"/>
+      <c r="AG57" s="2"/>
+      <c r="AH57" s="2"/>
+      <c r="AI57" s="2"/>
+      <c r="AJ57" s="2"/>
+      <c r="AK57" s="2"/>
+      <c r="AL57" s="2"/>
+      <c r="AM57" s="2"/>
+      <c r="AN57" s="2"/>
+      <c r="AO57" s="2"/>
+      <c r="AP57" s="2"/>
+      <c r="AQ57" s="2"/>
+      <c r="AR57" s="2"/>
+      <c r="AS57" s="2"/>
+      <c r="AT57" s="2"/>
+      <c r="AU57" s="2"/>
+      <c r="AV57" s="2"/>
+      <c r="AW57" s="2"/>
+      <c r="AX57" s="2"/>
+      <c r="AY57" s="2"/>
+      <c r="AZ57" s="2"/>
+      <c r="BA57" s="2"/>
+      <c r="BB57" s="2"/>
+      <c r="BC57" s="2"/>
+      <c r="BD57" s="2"/>
+      <c r="BE57" s="2"/>
+      <c r="BF57" s="2"/>
+      <c r="BG57" s="2"/>
+      <c r="BH57" s="2"/>
+      <c r="BI57" s="2"/>
+      <c r="BJ57" s="2"/>
+      <c r="BK57" s="2"/>
+      <c r="BL57" s="2"/>
+      <c r="BM57" s="2"/>
+      <c r="BN57" s="2"/>
+      <c r="BO57" s="2"/>
+      <c r="BP57" s="2"/>
+      <c r="BQ57" s="2"/>
+      <c r="BR57" s="2"/>
+      <c r="BS57" s="2"/>
+      <c r="BT57" s="2"/>
+    </row>
+    <row r="58" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="2"/>
-      <c r="T56" s="2"/>
-      <c r="U56" s="2"/>
-      <c r="V56" s="2"/>
-      <c r="W56" s="2"/>
-      <c r="X56" s="2"/>
-      <c r="Y56" s="2"/>
-      <c r="Z56" s="2"/>
-      <c r="AA56" s="2"/>
-      <c r="AB56" s="2"/>
-      <c r="AC56" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="2"/>
-      <c r="AE56" s="2"/>
-      <c r="AF56" s="2"/>
-      <c r="AG56" s="2"/>
-      <c r="AH56" s="2"/>
-      <c r="AI56" s="2"/>
-      <c r="AJ56" s="2"/>
-      <c r="AK56" s="2"/>
-      <c r="AL56" s="2"/>
-      <c r="AM56" s="2"/>
-      <c r="AN56" s="2"/>
-      <c r="AO56" s="2"/>
-      <c r="AP56" s="2"/>
-      <c r="AQ56" s="2"/>
-      <c r="AR56" s="2"/>
-      <c r="AS56" s="2"/>
-      <c r="AT56" s="2"/>
-      <c r="AU56" s="2"/>
-      <c r="AV56" s="2"/>
-      <c r="AW56" s="2"/>
-      <c r="AX56" s="2"/>
-      <c r="AY56" s="2"/>
-      <c r="AZ56" s="2"/>
-      <c r="BA56" s="2"/>
-      <c r="BB56" s="2"/>
-      <c r="BC56" s="2"/>
-      <c r="BD56" s="2"/>
-      <c r="BE56" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF56" s="2">
-        <v>1</v>
-      </c>
-      <c r="BG56" s="2"/>
-      <c r="BH56" s="2"/>
-      <c r="BI56" s="2"/>
-      <c r="BJ56" s="2"/>
-      <c r="BK56" s="2"/>
-      <c r="BL56" s="2"/>
-      <c r="BM56" s="2"/>
-      <c r="BN56" s="2"/>
-      <c r="BO56" s="2"/>
-      <c r="BP56" s="2"/>
-      <c r="BQ56" s="2"/>
-      <c r="BR56" s="2"/>
-    </row>
-    <row r="57" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A57" s="3" t="s">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
+      <c r="Y58" s="2"/>
+      <c r="Z58" s="2"/>
+      <c r="AA58" s="2"/>
+      <c r="AB58" s="2"/>
+      <c r="AC58" s="2"/>
+      <c r="AD58" s="2"/>
+      <c r="AE58" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="2"/>
+      <c r="AG58" s="2"/>
+      <c r="AH58" s="2"/>
+      <c r="AI58" s="2"/>
+      <c r="AJ58" s="2"/>
+      <c r="AK58" s="2"/>
+      <c r="AL58" s="2"/>
+      <c r="AM58" s="2"/>
+      <c r="AN58" s="2"/>
+      <c r="AO58" s="2"/>
+      <c r="AP58" s="2"/>
+      <c r="AQ58" s="2"/>
+      <c r="AR58" s="2"/>
+      <c r="AS58" s="2"/>
+      <c r="AT58" s="2"/>
+      <c r="AU58" s="2"/>
+      <c r="AV58" s="2"/>
+      <c r="AW58" s="2"/>
+      <c r="AX58" s="2"/>
+      <c r="AY58" s="2"/>
+      <c r="AZ58" s="2"/>
+      <c r="BA58" s="2"/>
+      <c r="BB58" s="2"/>
+      <c r="BC58" s="2"/>
+      <c r="BD58" s="2"/>
+      <c r="BE58" s="2"/>
+      <c r="BF58" s="2"/>
+      <c r="BG58" s="2">
+        <v>1</v>
+      </c>
+      <c r="BH58" s="2">
+        <v>1</v>
+      </c>
+      <c r="BI58" s="2"/>
+      <c r="BJ58" s="2"/>
+      <c r="BK58" s="2"/>
+      <c r="BL58" s="2"/>
+      <c r="BM58" s="2"/>
+      <c r="BN58" s="2"/>
+      <c r="BO58" s="2"/>
+      <c r="BP58" s="2"/>
+      <c r="BQ58" s="2"/>
+      <c r="BR58" s="2"/>
+      <c r="BS58" s="2"/>
+      <c r="BT58" s="2"/>
+    </row>
+    <row r="59" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A59" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
-      <c r="AB57" s="3"/>
-      <c r="AC57" s="3"/>
-      <c r="AD57" s="3"/>
-      <c r="AE57" s="3"/>
-      <c r="AF57" s="3"/>
-      <c r="AG57" s="3"/>
-      <c r="AH57" s="3"/>
-      <c r="AI57" s="3"/>
-      <c r="AJ57" s="3"/>
-      <c r="AK57" s="3"/>
-      <c r="AL57" s="3"/>
-      <c r="AM57" s="3"/>
-      <c r="AN57" s="3"/>
-      <c r="AO57" s="3"/>
-      <c r="AP57" s="3"/>
-      <c r="AQ57" s="3"/>
-      <c r="AR57" s="3"/>
-      <c r="AS57" s="3"/>
-      <c r="AT57" s="3"/>
-      <c r="AU57" s="3"/>
-      <c r="AV57" s="3"/>
-      <c r="AW57" s="3"/>
-      <c r="AX57" s="3"/>
-      <c r="AY57" s="3"/>
-      <c r="AZ57" s="3"/>
-      <c r="BA57" s="3"/>
-      <c r="BB57" s="3"/>
-      <c r="BC57" s="3"/>
-      <c r="BD57" s="3"/>
-      <c r="BE57" s="3"/>
-      <c r="BF57" s="3">
-        <v>1</v>
-      </c>
-      <c r="BG57" s="3"/>
-      <c r="BH57" s="3"/>
-      <c r="BI57" s="3"/>
-      <c r="BJ57" s="3"/>
-      <c r="BK57" s="3"/>
-      <c r="BL57" s="3"/>
-      <c r="BM57" s="3"/>
-      <c r="BN57" s="3"/>
-      <c r="BO57" s="3"/>
-      <c r="BP57" s="3"/>
-      <c r="BQ57" s="3"/>
-      <c r="BR57" s="3"/>
-    </row>
-    <row r="58" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A59" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -4440,9 +4618,7 @@
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
-      <c r="M59" s="3">
-        <v>1</v>
-      </c>
+      <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
@@ -4502,558 +4678,669 @@
       <c r="BP59" s="3"/>
       <c r="BQ59" s="3"/>
       <c r="BR59" s="3"/>
-    </row>
-    <row r="60" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A60" s="2" t="s">
+      <c r="BS59" s="3"/>
+      <c r="BT59" s="3"/>
+    </row>
+    <row r="60" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3">
+        <v>1</v>
+      </c>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+      <c r="AI61" s="3"/>
+      <c r="AJ61" s="3"/>
+      <c r="AK61" s="3"/>
+      <c r="AL61" s="3"/>
+      <c r="AM61" s="3"/>
+      <c r="AN61" s="3"/>
+      <c r="AO61" s="3"/>
+      <c r="AP61" s="3"/>
+      <c r="AQ61" s="3"/>
+      <c r="AR61" s="3"/>
+      <c r="AS61" s="3"/>
+      <c r="AT61" s="3"/>
+      <c r="AU61" s="3"/>
+      <c r="AV61" s="3"/>
+      <c r="AW61" s="3"/>
+      <c r="AX61" s="3"/>
+      <c r="AY61" s="3"/>
+      <c r="AZ61" s="3"/>
+      <c r="BA61" s="3"/>
+      <c r="BB61" s="3"/>
+      <c r="BC61" s="3"/>
+      <c r="BD61" s="3"/>
+      <c r="BE61" s="3"/>
+      <c r="BF61" s="3"/>
+      <c r="BG61" s="3"/>
+      <c r="BH61" s="3"/>
+      <c r="BI61" s="3"/>
+      <c r="BJ61" s="3">
+        <v>1</v>
+      </c>
+      <c r="BK61" s="3"/>
+      <c r="BL61" s="3"/>
+      <c r="BM61" s="3"/>
+      <c r="BN61" s="3"/>
+      <c r="BO61" s="3"/>
+      <c r="BP61" s="3"/>
+      <c r="BQ61" s="3"/>
+      <c r="BR61" s="3"/>
+      <c r="BS61" s="3"/>
+      <c r="BT61" s="3"/>
+    </row>
+    <row r="62" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="2"/>
-      <c r="V60" s="2"/>
-      <c r="W60" s="2"/>
-      <c r="X60" s="2"/>
-      <c r="Y60" s="2"/>
-      <c r="Z60" s="2"/>
-      <c r="AA60" s="2"/>
-      <c r="AB60" s="2"/>
-      <c r="AC60" s="2"/>
-      <c r="AD60" s="2"/>
-      <c r="AE60" s="2"/>
-      <c r="AF60" s="2"/>
-      <c r="AG60" s="2"/>
-      <c r="AH60" s="2"/>
-      <c r="AI60" s="2"/>
-      <c r="AJ60" s="2"/>
-      <c r="AK60" s="2"/>
-      <c r="AL60" s="2"/>
-      <c r="AM60" s="2"/>
-      <c r="AN60" s="2"/>
-      <c r="AO60" s="2"/>
-      <c r="AP60" s="2"/>
-      <c r="AQ60" s="2"/>
-      <c r="AR60" s="2"/>
-      <c r="AS60" s="2"/>
-      <c r="AT60" s="2"/>
-      <c r="AU60" s="2"/>
-      <c r="AV60" s="2"/>
-      <c r="AW60" s="2"/>
-      <c r="AX60" s="2"/>
-      <c r="AY60" s="2"/>
-      <c r="AZ60" s="2"/>
-      <c r="BA60" s="2"/>
-      <c r="BB60" s="2"/>
-      <c r="BC60" s="2"/>
-      <c r="BD60" s="2"/>
-      <c r="BE60" s="2"/>
-      <c r="BF60" s="2"/>
-      <c r="BG60" s="2"/>
-      <c r="BH60" s="2"/>
-      <c r="BI60" s="2"/>
-      <c r="BJ60" s="2"/>
-      <c r="BK60" s="2"/>
-      <c r="BL60" s="2"/>
-      <c r="BM60" s="2"/>
-      <c r="BN60" s="2"/>
-      <c r="BO60" s="2"/>
-      <c r="BP60" s="2"/>
-      <c r="BQ60" s="2"/>
-      <c r="BR60" s="2"/>
-    </row>
-    <row r="61" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
+      <c r="Y62" s="2"/>
+      <c r="Z62" s="2"/>
+      <c r="AA62" s="2"/>
+      <c r="AB62" s="2"/>
+      <c r="AC62" s="2"/>
+      <c r="AD62" s="2"/>
+      <c r="AE62" s="2"/>
+      <c r="AF62" s="2"/>
+      <c r="AG62" s="2"/>
+      <c r="AH62" s="2"/>
+      <c r="AI62" s="2"/>
+      <c r="AJ62" s="2"/>
+      <c r="AK62" s="2"/>
+      <c r="AL62" s="2"/>
+      <c r="AM62" s="2"/>
+      <c r="AN62" s="2"/>
+      <c r="AO62" s="2"/>
+      <c r="AP62" s="2"/>
+      <c r="AQ62" s="2"/>
+      <c r="AR62" s="2"/>
+      <c r="AS62" s="2"/>
+      <c r="AT62" s="2"/>
+      <c r="AU62" s="2"/>
+      <c r="AV62" s="2"/>
+      <c r="AW62" s="2"/>
+      <c r="AX62" s="2"/>
+      <c r="AY62" s="2"/>
+      <c r="AZ62" s="2"/>
+      <c r="BA62" s="2"/>
+      <c r="BB62" s="2"/>
+      <c r="BC62" s="2"/>
+      <c r="BD62" s="2"/>
+      <c r="BE62" s="2"/>
+      <c r="BF62" s="2"/>
+      <c r="BG62" s="2"/>
+      <c r="BH62" s="2"/>
+      <c r="BI62" s="2"/>
+      <c r="BJ62" s="2"/>
+      <c r="BK62" s="2"/>
+      <c r="BL62" s="2"/>
+      <c r="BM62" s="2"/>
+      <c r="BN62" s="2"/>
+      <c r="BO62" s="2"/>
+      <c r="BP62" s="2"/>
+      <c r="BQ62" s="2"/>
+      <c r="BR62" s="2"/>
+      <c r="BS62" s="2"/>
+      <c r="BT62" s="2"/>
+    </row>
+    <row r="63" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
         <v>67</v>
       </c>
-      <c r="BJ61">
-        <v>1</v>
-      </c>
-      <c r="BK61">
-        <v>1</v>
-      </c>
-      <c r="BL61">
-        <v>1</v>
-      </c>
-      <c r="BM61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A62" t="s">
+      <c r="BL63">
+        <v>1</v>
+      </c>
+      <c r="BM63">
+        <v>1</v>
+      </c>
+      <c r="BN63">
+        <v>1</v>
+      </c>
+      <c r="BO63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A63" s="2" t="s">
+    <row r="65" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A65" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
-      <c r="Y63" s="2"/>
-      <c r="Z63" s="2"/>
-      <c r="AA63" s="2"/>
-      <c r="AB63" s="2"/>
-      <c r="AC63" s="2"/>
-      <c r="AD63" s="2"/>
-      <c r="AE63" s="2"/>
-      <c r="AF63" s="2"/>
-      <c r="AG63" s="2"/>
-      <c r="AH63" s="2"/>
-      <c r="AI63" s="2"/>
-      <c r="AJ63" s="2"/>
-      <c r="AK63" s="2"/>
-      <c r="AL63" s="2"/>
-      <c r="AM63" s="2"/>
-      <c r="AN63" s="2"/>
-      <c r="AO63" s="2"/>
-      <c r="AP63" s="2"/>
-      <c r="AQ63" s="2"/>
-      <c r="AR63" s="2"/>
-      <c r="AS63" s="2"/>
-      <c r="AT63" s="2"/>
-      <c r="AU63" s="2"/>
-      <c r="AV63" s="2"/>
-      <c r="AW63" s="2"/>
-      <c r="AX63" s="2"/>
-      <c r="AY63" s="2"/>
-      <c r="AZ63" s="2"/>
-      <c r="BA63" s="2"/>
-      <c r="BB63" s="2"/>
-      <c r="BC63" s="2"/>
-      <c r="BD63" s="2"/>
-      <c r="BE63" s="2"/>
-      <c r="BF63" s="2"/>
-      <c r="BG63" s="2"/>
-      <c r="BH63" s="2"/>
-      <c r="BI63" s="2"/>
-      <c r="BJ63" s="2"/>
-      <c r="BK63" s="2"/>
-      <c r="BL63" s="2"/>
-      <c r="BM63" s="2"/>
-      <c r="BN63" s="2"/>
-      <c r="BO63" s="2"/>
-      <c r="BP63" s="2"/>
-      <c r="BQ63" s="2"/>
-      <c r="BR63" s="2"/>
-    </row>
-    <row r="64" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
+      <c r="Y65" s="2"/>
+      <c r="Z65" s="2"/>
+      <c r="AA65" s="2"/>
+      <c r="AB65" s="2"/>
+      <c r="AC65" s="2"/>
+      <c r="AD65" s="2"/>
+      <c r="AE65" s="2"/>
+      <c r="AF65" s="2"/>
+      <c r="AG65" s="2"/>
+      <c r="AH65" s="2"/>
+      <c r="AI65" s="2"/>
+      <c r="AJ65" s="2"/>
+      <c r="AK65" s="2"/>
+      <c r="AL65" s="2"/>
+      <c r="AM65" s="2"/>
+      <c r="AN65" s="2"/>
+      <c r="AO65" s="2"/>
+      <c r="AP65" s="2"/>
+      <c r="AQ65" s="2"/>
+      <c r="AR65" s="2"/>
+      <c r="AS65" s="2"/>
+      <c r="AT65" s="2"/>
+      <c r="AU65" s="2"/>
+      <c r="AV65" s="2"/>
+      <c r="AW65" s="2"/>
+      <c r="AX65" s="2"/>
+      <c r="AY65" s="2"/>
+      <c r="AZ65" s="2"/>
+      <c r="BA65" s="2"/>
+      <c r="BB65" s="2"/>
+      <c r="BC65" s="2"/>
+      <c r="BD65" s="2"/>
+      <c r="BE65" s="2"/>
+      <c r="BF65" s="2"/>
+      <c r="BG65" s="2"/>
+      <c r="BH65" s="2"/>
+      <c r="BI65" s="2"/>
+      <c r="BJ65" s="2"/>
+      <c r="BK65" s="2"/>
+      <c r="BL65" s="2"/>
+      <c r="BM65" s="2"/>
+      <c r="BN65" s="2"/>
+      <c r="BO65" s="2"/>
+      <c r="BP65" s="2"/>
+      <c r="BQ65" s="2"/>
+      <c r="BR65" s="2"/>
+      <c r="BS65" s="2"/>
+      <c r="BT65" s="2"/>
+    </row>
+    <row r="66" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
+    <row r="67" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
+    <row r="68" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
         <v>30</v>
       </c>
-      <c r="BQ66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A67" t="s">
+      <c r="BS68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A69" t="s">
         <v>28</v>
       </c>
-      <c r="S67">
-        <v>1</v>
-      </c>
-      <c r="AC67">
-        <v>1</v>
-      </c>
-      <c r="AI67">
-        <v>1</v>
-      </c>
-      <c r="BN67">
-        <v>1</v>
-      </c>
-      <c r="BQ67">
-        <v>1</v>
-      </c>
-      <c r="BR67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A68" s="2" t="s">
+      <c r="U69">
+        <v>1</v>
+      </c>
+      <c r="AE69">
+        <v>1</v>
+      </c>
+      <c r="AK69">
+        <v>1</v>
+      </c>
+      <c r="BP69">
+        <v>1</v>
+      </c>
+      <c r="BS69">
+        <v>1</v>
+      </c>
+      <c r="BT69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A70" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2">
-        <v>1</v>
-      </c>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
-      <c r="Y68" s="2"/>
-      <c r="Z68" s="2"/>
-      <c r="AA68" s="2"/>
-      <c r="AB68" s="2"/>
-      <c r="AC68" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD68" s="2"/>
-      <c r="AE68" s="2"/>
-      <c r="AF68" s="2"/>
-      <c r="AG68" s="2"/>
-      <c r="AH68" s="2"/>
-      <c r="AI68" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ68" s="2"/>
-      <c r="AK68" s="2"/>
-      <c r="AL68" s="2"/>
-      <c r="AM68" s="2"/>
-      <c r="AN68" s="2"/>
-      <c r="AO68" s="2"/>
-      <c r="AP68" s="2"/>
-      <c r="AQ68" s="2"/>
-      <c r="AR68" s="2"/>
-      <c r="AS68" s="2"/>
-      <c r="AT68" s="2"/>
-      <c r="AU68" s="2"/>
-      <c r="AV68" s="2"/>
-      <c r="AW68" s="2"/>
-      <c r="AX68" s="2"/>
-      <c r="AY68" s="2"/>
-      <c r="AZ68" s="2"/>
-      <c r="BA68" s="2"/>
-      <c r="BB68" s="2"/>
-      <c r="BC68" s="2"/>
-      <c r="BD68" s="2"/>
-      <c r="BE68" s="2"/>
-      <c r="BF68" s="2"/>
-      <c r="BG68" s="2"/>
-      <c r="BH68" s="2"/>
-      <c r="BI68" s="2"/>
-      <c r="BJ68" s="2"/>
-      <c r="BK68" s="2"/>
-      <c r="BL68" s="2"/>
-      <c r="BM68" s="2"/>
-      <c r="BN68" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO68" s="2"/>
-      <c r="BP68" s="2"/>
-      <c r="BQ68" s="2">
-        <v>1</v>
-      </c>
-      <c r="BR68" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:70" x14ac:dyDescent="0.45">
-      <c r="A69" s="2" t="s">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2">
+        <v>1</v>
+      </c>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+      <c r="Y70" s="2"/>
+      <c r="Z70" s="2"/>
+      <c r="AA70" s="2"/>
+      <c r="AB70" s="2"/>
+      <c r="AC70" s="2"/>
+      <c r="AD70" s="2"/>
+      <c r="AE70" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="2"/>
+      <c r="AG70" s="2"/>
+      <c r="AH70" s="2"/>
+      <c r="AI70" s="2"/>
+      <c r="AJ70" s="2"/>
+      <c r="AK70" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL70" s="2"/>
+      <c r="AM70" s="2"/>
+      <c r="AN70" s="2"/>
+      <c r="AO70" s="2"/>
+      <c r="AP70" s="2"/>
+      <c r="AQ70" s="2"/>
+      <c r="AR70" s="2"/>
+      <c r="AS70" s="2"/>
+      <c r="AT70" s="2"/>
+      <c r="AU70" s="2"/>
+      <c r="AV70" s="2"/>
+      <c r="AW70" s="2"/>
+      <c r="AX70" s="2"/>
+      <c r="AY70" s="2"/>
+      <c r="AZ70" s="2"/>
+      <c r="BA70" s="2"/>
+      <c r="BB70" s="2"/>
+      <c r="BC70" s="2"/>
+      <c r="BD70" s="2"/>
+      <c r="BE70" s="2"/>
+      <c r="BF70" s="2"/>
+      <c r="BG70" s="2"/>
+      <c r="BH70" s="2"/>
+      <c r="BI70" s="2"/>
+      <c r="BJ70" s="2"/>
+      <c r="BK70" s="2"/>
+      <c r="BL70" s="2"/>
+      <c r="BM70" s="2"/>
+      <c r="BN70" s="2"/>
+      <c r="BO70" s="2"/>
+      <c r="BP70" s="2">
+        <v>1</v>
+      </c>
+      <c r="BQ70" s="2"/>
+      <c r="BR70" s="2"/>
+      <c r="BS70" s="2">
+        <v>1</v>
+      </c>
+      <c r="BT70" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:72" x14ac:dyDescent="0.45">
+      <c r="A71" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2">
-        <v>1</v>
-      </c>
-      <c r="T69" s="2"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
-      <c r="Y69" s="2"/>
-      <c r="Z69" s="2"/>
-      <c r="AA69" s="2"/>
-      <c r="AB69" s="2"/>
-      <c r="AC69" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD69" s="2"/>
-      <c r="AE69" s="2"/>
-      <c r="AF69" s="2"/>
-      <c r="AG69" s="2"/>
-      <c r="AH69" s="2"/>
-      <c r="AI69" s="2"/>
-      <c r="AJ69" s="2"/>
-      <c r="AK69" s="2"/>
-      <c r="AL69" s="2"/>
-      <c r="AM69" s="2"/>
-      <c r="AN69" s="2"/>
-      <c r="AO69" s="2"/>
-      <c r="AP69" s="2"/>
-      <c r="AQ69" s="2"/>
-      <c r="AR69" s="2"/>
-      <c r="AS69" s="2"/>
-      <c r="AT69" s="2"/>
-      <c r="AU69" s="2"/>
-      <c r="AV69" s="2"/>
-      <c r="AW69" s="2"/>
-      <c r="AX69" s="2"/>
-      <c r="AY69" s="2"/>
-      <c r="AZ69" s="2"/>
-      <c r="BA69" s="2"/>
-      <c r="BB69" s="2"/>
-      <c r="BC69" s="2"/>
-      <c r="BD69" s="2"/>
-      <c r="BE69" s="2"/>
-      <c r="BF69" s="2"/>
-      <c r="BG69" s="2"/>
-      <c r="BH69" s="2"/>
-      <c r="BI69" s="2"/>
-      <c r="BJ69" s="2"/>
-      <c r="BK69" s="2"/>
-      <c r="BL69" s="2"/>
-      <c r="BM69" s="2"/>
-      <c r="BN69" s="2"/>
-      <c r="BO69" s="2"/>
-      <c r="BP69" s="2"/>
-      <c r="BQ69" s="2"/>
-      <c r="BR69" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A70" s="3" t="s">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2">
+        <v>1</v>
+      </c>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
+      <c r="Y71" s="2"/>
+      <c r="Z71" s="2"/>
+      <c r="AA71" s="2"/>
+      <c r="AB71" s="2"/>
+      <c r="AC71" s="2"/>
+      <c r="AD71" s="2"/>
+      <c r="AE71" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF71" s="2"/>
+      <c r="AG71" s="2"/>
+      <c r="AH71" s="2"/>
+      <c r="AI71" s="2"/>
+      <c r="AJ71" s="2"/>
+      <c r="AK71" s="2"/>
+      <c r="AL71" s="2"/>
+      <c r="AM71" s="2"/>
+      <c r="AN71" s="2"/>
+      <c r="AO71" s="2"/>
+      <c r="AP71" s="2"/>
+      <c r="AQ71" s="2"/>
+      <c r="AR71" s="2"/>
+      <c r="AS71" s="2"/>
+      <c r="AT71" s="2"/>
+      <c r="AU71" s="2"/>
+      <c r="AV71" s="2"/>
+      <c r="AW71" s="2"/>
+      <c r="AX71" s="2"/>
+      <c r="AY71" s="2"/>
+      <c r="AZ71" s="2"/>
+      <c r="BA71" s="2"/>
+      <c r="BB71" s="2"/>
+      <c r="BC71" s="2"/>
+      <c r="BD71" s="2"/>
+      <c r="BE71" s="2"/>
+      <c r="BF71" s="2"/>
+      <c r="BG71" s="2"/>
+      <c r="BH71" s="2"/>
+      <c r="BI71" s="2"/>
+      <c r="BJ71" s="2"/>
+      <c r="BK71" s="2"/>
+      <c r="BL71" s="2"/>
+      <c r="BM71" s="2"/>
+      <c r="BN71" s="2"/>
+      <c r="BO71" s="2"/>
+      <c r="BP71" s="2"/>
+      <c r="BQ71" s="2"/>
+      <c r="BR71" s="2"/>
+      <c r="BS71" s="2"/>
+      <c r="BT71" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A72" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
-      <c r="AB70" s="3"/>
-      <c r="AC70" s="3"/>
-      <c r="AD70" s="3"/>
-      <c r="AE70" s="3"/>
-      <c r="AF70" s="3"/>
-      <c r="AG70" s="3"/>
-      <c r="AH70" s="3"/>
-      <c r="AI70" s="3"/>
-      <c r="AJ70" s="3"/>
-      <c r="AK70" s="3"/>
-      <c r="AL70" s="3"/>
-      <c r="AM70" s="3"/>
-      <c r="AN70" s="3"/>
-      <c r="AO70" s="3"/>
-      <c r="AP70" s="3"/>
-      <c r="AQ70" s="3"/>
-      <c r="AR70" s="3"/>
-      <c r="AS70" s="3"/>
-      <c r="AT70" s="3"/>
-      <c r="AU70" s="3"/>
-      <c r="AV70" s="3"/>
-      <c r="AW70" s="3"/>
-      <c r="AX70" s="3"/>
-      <c r="AY70" s="3"/>
-      <c r="AZ70" s="3"/>
-      <c r="BA70" s="3"/>
-      <c r="BB70" s="3"/>
-      <c r="BC70" s="3"/>
-      <c r="BD70" s="3"/>
-      <c r="BE70" s="3"/>
-      <c r="BF70" s="3"/>
-      <c r="BG70" s="3"/>
-      <c r="BH70" s="3"/>
-      <c r="BI70" s="3"/>
-      <c r="BJ70" s="3"/>
-      <c r="BK70" s="3"/>
-      <c r="BL70" s="3"/>
-      <c r="BM70" s="3"/>
-      <c r="BN70" s="3"/>
-      <c r="BO70" s="3"/>
-      <c r="BP70" s="3"/>
-      <c r="BQ70" s="3"/>
-      <c r="BR70" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
+      <c r="AB72" s="3"/>
+      <c r="AC72" s="3"/>
+      <c r="AD72" s="3"/>
+      <c r="AE72" s="3"/>
+      <c r="AF72" s="3"/>
+      <c r="AG72" s="3"/>
+      <c r="AH72" s="3"/>
+      <c r="AI72" s="3"/>
+      <c r="AJ72" s="3"/>
+      <c r="AK72" s="3"/>
+      <c r="AL72" s="3"/>
+      <c r="AM72" s="3"/>
+      <c r="AN72" s="3"/>
+      <c r="AO72" s="3"/>
+      <c r="AP72" s="3"/>
+      <c r="AQ72" s="3"/>
+      <c r="AR72" s="3"/>
+      <c r="AS72" s="3"/>
+      <c r="AT72" s="3"/>
+      <c r="AU72" s="3"/>
+      <c r="AV72" s="3"/>
+      <c r="AW72" s="3"/>
+      <c r="AX72" s="3"/>
+      <c r="AY72" s="3"/>
+      <c r="AZ72" s="3"/>
+      <c r="BA72" s="3"/>
+      <c r="BB72" s="3"/>
+      <c r="BC72" s="3"/>
+      <c r="BD72" s="3"/>
+      <c r="BE72" s="3"/>
+      <c r="BF72" s="3"/>
+      <c r="BG72" s="3"/>
+      <c r="BH72" s="3"/>
+      <c r="BI72" s="3"/>
+      <c r="BJ72" s="3"/>
+      <c r="BK72" s="3"/>
+      <c r="BL72" s="3"/>
+      <c r="BM72" s="3"/>
+      <c r="BN72" s="3"/>
+      <c r="BO72" s="3"/>
+      <c r="BP72" s="3"/>
+      <c r="BQ72" s="3"/>
+      <c r="BR72" s="3"/>
+      <c r="BS72" s="3"/>
+      <c r="BT72" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR70" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}"/>
-  <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="66" priority="1580"/>
+  <autoFilter ref="A1:BT72" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}"/>
+  <conditionalFormatting sqref="A4:C5">
+    <cfRule type="duplicateValues" dxfId="70" priority="1584"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A70 B1:BR1">
-    <cfRule type="duplicateValues" dxfId="65" priority="1638"/>
+  <conditionalFormatting sqref="A4:C72 D1:BT1 L2:BT3">
+    <cfRule type="duplicateValues" dxfId="69" priority="1642"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="64" priority="1574"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="1581"/>
+  <conditionalFormatting sqref="A6:C6">
+    <cfRule type="duplicateValues" dxfId="68" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1585"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="62" priority="1582"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="1575"/>
+  <conditionalFormatting sqref="A7:C7">
+    <cfRule type="duplicateValues" dxfId="66" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1586"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="60" priority="1583"/>
+  <conditionalFormatting sqref="A8:C8">
+    <cfRule type="duplicateValues" dxfId="64" priority="1587"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="59" priority="1584"/>
+  <conditionalFormatting sqref="A9:C9">
+    <cfRule type="duplicateValues" dxfId="63" priority="1588"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="58" priority="1585"/>
+  <conditionalFormatting sqref="A10:C10">
+    <cfRule type="duplicateValues" dxfId="62" priority="1589"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="57" priority="1586"/>
+  <conditionalFormatting sqref="A11:C11">
+    <cfRule type="duplicateValues" dxfId="61" priority="1590"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="56" priority="1587"/>
+  <conditionalFormatting sqref="A12:C12">
+    <cfRule type="duplicateValues" dxfId="60" priority="1591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="55" priority="1588"/>
+  <conditionalFormatting sqref="A13:C13">
+    <cfRule type="duplicateValues" dxfId="59" priority="1592"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="54" priority="1589"/>
+  <conditionalFormatting sqref="A14:C14">
+    <cfRule type="duplicateValues" dxfId="58" priority="1593"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="53" priority="1590"/>
+  <conditionalFormatting sqref="A15:C15">
+    <cfRule type="duplicateValues" dxfId="57" priority="1594"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="52" priority="1591"/>
+  <conditionalFormatting sqref="A16:C16">
+    <cfRule type="duplicateValues" dxfId="56" priority="1595"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="51" priority="1592"/>
+  <conditionalFormatting sqref="A17:C17">
+    <cfRule type="duplicateValues" dxfId="55" priority="1596"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="50" priority="1593"/>
+  <conditionalFormatting sqref="A18:C18">
+    <cfRule type="duplicateValues" dxfId="54" priority="1597"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="49" priority="1594"/>
+  <conditionalFormatting sqref="A19:C19">
+    <cfRule type="duplicateValues" dxfId="53" priority="1598"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A25">
-    <cfRule type="duplicateValues" dxfId="48" priority="1596"/>
+  <conditionalFormatting sqref="A20:C27">
+    <cfRule type="duplicateValues" dxfId="52" priority="1600"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="47" priority="1597"/>
+  <conditionalFormatting sqref="A28:C28">
+    <cfRule type="duplicateValues" dxfId="51" priority="1601"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A35">
-    <cfRule type="duplicateValues" dxfId="46" priority="1598"/>
+  <conditionalFormatting sqref="A29:C37">
+    <cfRule type="duplicateValues" dxfId="50" priority="1602"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A36:A43">
-    <cfRule type="duplicateValues" dxfId="45" priority="1599"/>
+  <conditionalFormatting sqref="A38:C45">
+    <cfRule type="duplicateValues" dxfId="49" priority="1603"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="44" priority="1600"/>
+  <conditionalFormatting sqref="A46:C46">
+    <cfRule type="duplicateValues" dxfId="48" priority="1604"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="43" priority="1601"/>
+  <conditionalFormatting sqref="A47:C47">
+    <cfRule type="duplicateValues" dxfId="47" priority="1605"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46:A49">
-    <cfRule type="duplicateValues" dxfId="42" priority="1576"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="1578"/>
+  <conditionalFormatting sqref="A48:C51">
+    <cfRule type="duplicateValues" dxfId="46" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1582"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="40" priority="1602"/>
+  <conditionalFormatting sqref="A52:C52">
+    <cfRule type="duplicateValues" dxfId="44" priority="1606"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A51:A70">
-    <cfRule type="duplicateValues" dxfId="39" priority="1603"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="1627"/>
+  <conditionalFormatting sqref="A53:C72">
+    <cfRule type="duplicateValues" dxfId="43" priority="1607"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1631"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:BR1">
-    <cfRule type="duplicateValues" dxfId="37" priority="1631"/>
+  <conditionalFormatting sqref="D1:BT1 L2:BT3">
+    <cfRule type="duplicateValues" dxfId="41" priority="1635"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BS1048576">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+  <conditionalFormatting sqref="D1048576:BU1048576 L4:BU1048575">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE1:AF1">
-    <cfRule type="duplicateValues" dxfId="34" priority="14"/>
+  <conditionalFormatting sqref="AG1:AH3">
+    <cfRule type="duplicateValues" dxfId="38" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF1">
-    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
+  <conditionalFormatting sqref="AH1:AH3">
+    <cfRule type="duplicateValues" dxfId="37" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH1">
-    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+  <conditionalFormatting sqref="AJ1:AJ3">
+    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:K3">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:K3">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:K1048575">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9228,92 +9515,92 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="31" priority="1406"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="30" priority="1400"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="1407"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="28" priority="1401"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="1408"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="26" priority="1409"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="25" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="24" priority="1411"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="23" priority="1412"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="22" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="21" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="20" priority="1415"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="19" priority="1416"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="18" priority="1417"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="17" priority="1418"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="16" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="15" priority="1420"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="14" priority="1421"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A27">
-    <cfRule type="duplicateValues" dxfId="13" priority="1422"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="12" priority="1423"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:A36">
-    <cfRule type="duplicateValues" dxfId="11" priority="1424"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:A44">
-    <cfRule type="duplicateValues" dxfId="10" priority="1425"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="9" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="8" priority="1427"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A50">
-    <cfRule type="duplicateValues" dxfId="7" priority="1402"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1404"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1402"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="5" priority="1428"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:A72">
-    <cfRule type="duplicateValues" dxfId="4" priority="1429"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1429"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:BT1 A2:A72">
-    <cfRule type="duplicateValues" dxfId="2" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:BT1">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:BU1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
